--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>76.84634399414062</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78.16999816894531</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.323654174804688</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.693302041460885</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9823316354755363</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>78.20375061035156</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>76.795959,76.802383,76.824715,76.824722,76.860756,76.860390,76.933151,76.901466,76.914917,76.911919,76.930954,76.938118,76.936752,76.904190,76.955315,76.897850,76.963112,76.951881,76.899704,76.898560,76.863167,76.887886,76.873047,76.846344</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>76.430000,75.849998,75.570000,76.150002,76.080002,76.400002,76.279999,77.070000,76.669998,76.209999,76.059998,77.720001,77.599998,77.680000,77.599998,77.570000,77.820000,77.699997,77.389999,77.790001,78.070000,77.779999,77.980003,78.169998</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.365959,0.952385,1.254715,0.674720,0.780754,0.460388,0.653152,0.168534,0.244919,0.701920,0.870956,0.781883,0.663246,0.775810,0.644683,0.672150,0.856888,0.748116,0.490295,0.891441,1.206833,0.892113,1.106956,1.323654</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.478816,1.255616,1.660335,0.886041,1.026228,0.602603,0.856256,0.218676,0.319445,0.921034,1.145091,1.006026,0.854699,0.998726,0.830778,0.866507,1.101115,0.962826,0.633538,1.145958,1.545834,1.146969,1.419539,1.693302</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9823316354755363</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>76.800598,76.731224,76.817787,76.773476,76.785789,76.754539,76.896004,76.880730,76.727562,76.955505,76.818726,76.873314,76.829178,76.868652,76.863396,76.873421,76.913338,76.785492,76.826180,76.913834,76.779915,76.830048,76.737747,76.764313</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>76.492821,76.487450,76.484657,76.358780,76.357407,76.264503,76.364410,76.224594,76.270569,76.142448,76.170029,76.221741,76.155670,75.911446,76.046997,75.914886,75.935005,75.906059,75.787659,75.726585,75.711304,75.705467,75.691498,75.608536</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>78.153618,78.140221,78.125389,78.152008,78.167000,78.189491,78.229851,78.220421,78.276405,78.264221,78.290047,78.310593,78.296593,78.257622,78.275665,78.219826,78.294479,78.261124,78.232941,78.237625,78.217552,78.265862,78.265617,78.203751</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>78.068604,78.095528,78.142426,78.094139,78.107727,78.106461,78.197266,78.249817,78.089302,78.285042,78.276337,78.253395,78.175262,78.159958,78.138741,78.173233,78.196213,78.144623,78.122429,78.231880,78.156151,78.154152,78.144508,78.102936</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>77.595467,77.460838,77.317085,77.255173,77.194054,77.073898,77.052048,76.922844,76.997803,76.862778,76.904587,76.742592,76.767670,76.539650,76.469559,76.348213,76.415131,76.335533,76.152191,76.041435,76.046822,76.003105,76.037521,75.899040</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>77.829903,77.724655,77.666252,77.625702,77.592575,77.494499,77.473999,77.383362,77.498154,77.363113,77.381683,77.375954,77.330658,77.176872,77.144791,77.071648,77.111969,77.036324,76.936905,76.928391,76.883606,76.847244,76.853645,76.764091</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>78.20375061035156</v>
+      </c>
+      <c r="G3" t="n">
+        <v>78.12999725341797</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.07375335693359375</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.09439825870513165</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3163396157356476</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:55</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>77.89380645751953</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>78.153618,78.140221,78.125389,78.152008,78.167000,78.189491,78.229851,78.220421,78.276405,78.264221,78.290047,78.310593,78.296593,78.257622,78.275665,78.219826,78.294479,78.261124,78.232941,78.237625,78.217552,78.265862,78.265617,78.203751</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78.080002,78.389999,78.610001,78.510002,78.300003,78.370003,78.160004,78.320000,78.459999,78.540001,77.940002,78.099998,78.160004,77.669998,77.820000,77.820000,77.879997,77.980003,77.949997,78.040001,78.430000,78.300003,78.080002,78.129997</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.073616,0.249778,0.484612,0.357994,0.133003,0.180512,0.069847,0.099579,0.183594,0.275780,0.350045,0.210595,0.136589,0.587624,0.455665,0.399826,0.414482,0.281121,0.282944,0.197624,0.212448,0.034141,0.185615,0.073754</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.094283,0.318636,0.616476,0.455985,0.169863,0.230333,0.089365,0.127143,0.233997,0.351133,0.449121,0.269647,0.174756,0.756565,0.585538,0.513783,0.532206,0.360504,0.362981,0.253234,0.270876,0.043603,0.237724,0.094399</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3163396157356476</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>78.068604,78.095528,78.142426,78.094139,78.107727,78.106461,78.197266,78.249817,78.089302,78.285042,78.276337,78.253395,78.175262,78.159958,78.138741,78.173233,78.196213,78.144623,78.122429,78.231880,78.156151,78.154152,78.144508,78.102936</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>77.829903,77.724655,77.666252,77.625702,77.592575,77.494499,77.473999,77.383362,77.498154,77.363113,77.381683,77.375954,77.330658,77.176872,77.144791,77.071648,77.111969,77.036324,76.936905,76.928391,76.883606,76.847244,76.853645,76.764091</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:55</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>78.109032,78.072830,78.094788,78.046989,78.046066,78.055534,78.088333,77.937126,78.003326,78.006508,78.013329,77.961784,77.996437,77.988197,77.967827,77.905334,78.010376,77.984680,77.910301,77.933662,77.922256,77.953224,77.905083,77.893806</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>78.025391,78.010643,78.084534,78.016434,77.928391,78.079781,77.989189,77.930946,77.951950,78.002151,78.017586,77.999352,77.849670,77.862343,77.815697,77.874435,77.921951,77.791336,77.840950,77.904869,77.822281,77.831970,77.845528,77.754448</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>77.681107,77.536491,77.431160,77.257042,77.185600,77.025871,76.979378,76.683395,76.806984,76.684494,76.725395,76.547394,76.686226,76.427269,76.341042,76.202408,76.248169,76.235916,75.981926,75.939148,75.929298,75.829865,75.820412,75.817535</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>77.833656,77.775780,77.748283,77.587097,77.511917,77.424332,77.429817,77.176422,77.300278,77.135002,77.179604,77.174156,77.144463,76.977455,76.946510,76.845551,76.925621,76.826965,76.708992,76.681328,76.674614,76.614342,76.580017,76.538651</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>77.89380645751953</v>
+      </c>
+      <c r="G4" t="n">
+        <v>77.61000061035156</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2838058471679688</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3656820576420856</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4753716843489782</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:54</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>77.44118499755859</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>78.109032,78.072830,78.094788,78.046989,78.046066,78.055534,78.088333,77.937126,78.003326,78.006508,78.013329,77.961784,77.996437,77.988197,77.967827,77.905334,78.010376,77.984680,77.910301,77.933662,77.922256,77.953224,77.905083,77.893806</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>78.019997,77.379997,77.250000,77.050003,77.379997,77.500000,77.620003,77.510002,77.180000,77.820000,77.849998,78.419998,78.550003,78.190002,77.720001,77.639999,77.769997,78.000000,77.989998,77.949997,78.230003,77.860001,77.730003,77.610001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.089035,0.692833,0.844788,0.996986,0.666069,0.555534,0.468330,0.427124,0.823326,0.186508,0.163331,0.458214,0.553566,0.201805,0.247826,0.265335,0.240379,0.015320,0.079697,0.016335,0.307747,0.093223,0.175080,0.283805</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.114119,0.895364,1.093577,1.293947,0.860776,0.716818,0.603363,0.551056,1.066760,0.239666,0.209802,0.584308,0.704731,0.258096,0.318870,0.341750,0.309090,0.019641,0.102189,0.020956,0.393388,0.119732,0.225241,0.365681</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4753716843489782</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>78.025391,78.010643,78.084534,78.016434,77.928391,78.079781,77.989189,77.930946,77.951950,78.002151,78.017586,77.999352,77.849670,77.862343,77.815697,77.874435,77.921951,77.791336,77.840950,77.904869,77.822281,77.831970,77.845528,77.754448</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>77.833656,77.775780,77.748283,77.587097,77.511917,77.424332,77.429817,77.176422,77.300278,77.135002,77.179604,77.174156,77.144463,76.977455,76.946510,76.845551,76.925621,76.826965,76.708992,76.681328,76.674614,76.614342,76.580017,76.538651</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:54</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>77.558472,77.512886,77.565056,77.544762,77.536469,77.553757,77.579376,77.514084,77.554588,77.544273,77.583481,77.557846,77.553673,77.555939,77.533241,77.480591,77.570808,77.536308,77.477402,77.484398,77.471741,77.491447,77.471016,77.441185</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>77.479576,77.447777,77.540802,77.501076,77.467201,77.557808,77.471085,77.576599,77.526459,77.486725,77.645569,77.476776,77.461021,77.467514,77.431313,77.403107,77.513496,77.354980,77.447594,77.400764,77.451248,77.351204,77.446762,77.436699</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>77.098808,76.883728,76.822151,76.781494,76.607826,76.497238,76.488098,76.346420,76.339684,76.235237,76.262802,76.233421,76.256935,76.066780,75.993736,75.910294,75.940071,75.940254,75.686226,75.668335,75.670685,75.557571,75.568962,75.601448</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>77.279251,77.147881,77.176521,77.057098,76.967995,76.898254,76.889847,76.750702,76.872444,76.699554,76.753609,76.776123,76.682495,76.558578,76.532028,76.446159,76.608917,76.458694,76.396233,76.308434,76.326027,76.263519,76.248611,76.221458</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>77.44118499755859</v>
+      </c>
+      <c r="G5" t="n">
+        <v>75.84999847412109</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5911865234375</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.097806928737632</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.393087952192905</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>75.41158294677734</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>77.558472,77.512886,77.565056,77.544762,77.536469,77.553757,77.579376,77.514084,77.554588,77.544273,77.583481,77.557846,77.553673,77.555939,77.533241,77.480591,77.570808,77.536308,77.477402,77.484398,77.471741,77.491447,77.471016,77.441185</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>77.470001,77.489998,77.540001,77.120003,77.430000,77.459999,77.709999,77.620003,76.889999,76.660004,76.379997,76.320000,75.930000,75.580002,75.730003,75.690002,76.070000,75.980003,76.129997,75.820000,75.779999,75.629997,75.470001,75.849998</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.088471,0.022888,0.025055,0.424759,0.106469,0.093758,0.130623,0.105919,0.664589,0.884269,1.203484,1.237846,1.623673,1.975937,1.803238,1.790589,1.500808,1.556305,1.347405,1.664398,1.691742,1.861450,2.001015,1.591187</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.114200,0.029537,0.032312,0.550777,0.137503,0.121040,0.168090,0.136458,0.864337,1.153495,1.575653,1.621916,2.138381,2.614365,2.381140,2.365687,1.972931,2.048308,1.769874,2.195197,2.232439,2.461259,2.651404,2.097807</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.393087952192905</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>77.479576,77.447777,77.540802,77.501076,77.467201,77.557808,77.471085,77.576599,77.526459,77.486725,77.645569,77.476776,77.461021,77.467514,77.431313,77.403107,77.513496,77.354980,77.447594,77.400764,77.451248,77.351204,77.446762,77.436699</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>77.279251,77.147881,77.176521,77.057098,76.967995,76.898254,76.889847,76.750702,76.872444,76.699554,76.753609,76.776123,76.682495,76.558578,76.532028,76.446159,76.608917,76.458694,76.396233,76.308434,76.326027,76.263519,76.248611,76.221458</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>75.804131,75.776459,75.752632,75.731171,75.703651,75.675972,75.646629,75.598877,75.630676,75.599373,75.579063,75.542397,75.561333,75.516571,75.503204,75.440002,75.490799,75.475288,75.431190,75.464905,75.464745,75.443024,75.440758,75.411583</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>75.741997,75.638229,75.733826,75.714081,75.687912,75.642296,75.600388,75.613686,75.577942,75.576653,75.621277,75.533104,75.532219,75.517563,75.531601,75.481735,75.535660,75.419838,75.504410,75.434006,75.474457,75.386086,75.489471,75.465424</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>75.255791,75.132729,74.994286,74.944046,74.798203,74.640518,74.606880,74.462433,74.417000,74.246330,74.248344,74.181114,74.175621,73.946899,73.925598,73.802673,73.769508,73.757935,73.507469,73.473671,73.411583,73.261581,73.235092,73.156113</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>75.448410,75.376564,75.318680,75.210617,75.141678,75.025192,74.985390,74.839165,74.906151,74.735001,74.710938,74.721741,74.660088,74.476944,74.534500,74.387230,74.421532,74.332436,74.247650,74.218475,74.182724,74.077309,74.077698,73.978119</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>75.41158294677734</v>
+      </c>
+      <c r="G6" t="n">
+        <v>74.19000244140625</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.221580505371094</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.646556766642342</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.434533149182724</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>73.82665252685547</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>75.804131,75.776459,75.752632,75.731171,75.703651,75.675972,75.646629,75.598877,75.630676,75.599373,75.579063,75.542397,75.561333,75.516571,75.503204,75.440002,75.490799,75.475288,75.431190,75.464905,75.464745,75.443024,75.440758,75.411583</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>75.610001,75.730003,75.790001,76.029999,75.720001,75.570000,75.430000,75.139999,74.800003,74.129997,73.980003,73.959999,73.839996,73.980003,73.910004,73.870003,73.709999,73.559998,73.870003,73.900002,74.070000,74.059998,74.050003,74.190002</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.194130,0.046456,0.037369,0.298828,0.016350,0.105972,0.216629,0.458878,0.830673,1.469376,1.599060,1.582398,1.721337,1.536568,1.593200,1.569999,1.780800,1.915290,1.561187,1.564903,1.394745,1.383026,1.390755,1.221581</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.256752,0.061344,0.049306,0.393039,0.021593,0.140231,0.287192,0.610697,1.110525,1.982161,2.161475,2.139532,2.331171,2.077004,2.155595,2.125354,2.415954,2.603712,2.113425,2.117596,1.883010,1.867441,1.878129,1.646557</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.434533149182724</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>75.741997,75.638229,75.733826,75.714081,75.687912,75.642296,75.600388,75.613686,75.577942,75.576653,75.621277,75.533104,75.532219,75.517563,75.531601,75.481735,75.535660,75.419838,75.504410,75.434006,75.474457,75.386086,75.489471,75.465424</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>75.448410,75.376564,75.318680,75.210617,75.141678,75.025192,74.985390,74.839165,74.906151,74.735001,74.710938,74.721741,74.660088,74.476944,74.534500,74.387230,74.421532,74.332436,74.247650,74.218475,74.182724,74.077309,74.077698,73.978119</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>74.243866,74.240334,74.247330,74.231453,74.229652,74.219391,74.190964,74.202782,74.182281,74.154976,74.102943,74.047539,74.038147,73.988777,73.968811,73.929039,73.901833,73.929260,73.836998,73.887543,73.904617,73.849930,73.866547,73.826653</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>74.149582,74.190720,74.190186,74.219864,74.199715,74.173843,74.213943,74.184120,74.186409,74.250244,74.166901,74.071243,74.075981,74.040909,74.043259,74.071831,74.082359,74.073723,74.011528,74.049088,73.948341,73.877098,73.986031,73.975945</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>73.852570,73.743958,73.584351,73.534798,73.454147,73.323601,73.273849,73.185249,73.103180,72.906311,72.875984,72.736526,72.678436,72.449142,72.416725,72.317757,72.216446,72.222855,71.881050,71.876884,71.811317,71.695999,71.722977,71.681709</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>73.944649,73.934875,73.864754,73.719612,73.716179,73.640427,73.636322,73.528275,73.516624,73.348488,73.231194,73.252548,73.135918,72.958740,73.043755,72.911766,72.854332,72.768730,72.629219,72.568298,72.563713,72.491173,72.542290,72.461426</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>73.82665252685547</v>
+      </c>
+      <c r="G7" t="n">
+        <v>74.91999816894531</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.093345642089844</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.459350866005548</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6083586206141277</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>75.06426239013672</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>74.243866,74.240334,74.247330,74.231453,74.229652,74.219391,74.190964,74.202782,74.182281,74.154976,74.102943,74.047539,74.038147,73.988777,73.968811,73.929039,73.901833,73.929260,73.836998,73.887543,73.904617,73.849930,73.866547,73.826653</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>74.250000,73.910004,73.970001,73.730003,73.739998,73.930000,73.919998,73.860001,73.900002,73.910004,73.980003,74.110001,74.260002,74.400002,74.599998,74.510002,74.389999,74.400002,74.440002,74.339996,74.720001,74.760002,74.830002,74.919998</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.006134,0.330330,0.277329,0.501450,0.489654,0.289391,0.270966,0.342781,0.282279,0.244972,0.122940,0.062462,0.221855,0.411225,0.631187,0.580963,0.488166,0.470742,0.603004,0.452453,0.815384,0.910072,0.963455,1.093345</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.008261,0.446936,0.374921,0.680116,0.664028,0.391439,0.366566,0.464096,0.381975,0.331447,0.166180,0.084282,0.298755,0.552721,0.846096,0.779712,0.656226,0.632717,0.810054,0.608627,1.091253,1.217325,1.287525,1.459350</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6083586206141277</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>74.149582,74.190720,74.190186,74.219864,74.199715,74.173843,74.213943,74.184120,74.186409,74.250244,74.166901,74.071243,74.075981,74.040909,74.043259,74.071831,74.082359,74.073723,74.011528,74.049088,73.948341,73.877098,73.986031,73.975945</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>73.944649,73.934875,73.864754,73.719612,73.716179,73.640427,73.636322,73.528275,73.516624,73.348488,73.231194,73.252548,73.135918,72.958740,73.043755,72.911766,72.854332,72.768730,72.629219,72.568298,72.563713,72.491173,72.542290,72.461426</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>74.965546,75.018051,75.008644,75.011971,75.041710,75.068489,75.053391,75.050659,75.072365,75.069351,75.048515,75.005714,75.060776,75.060280,75.083519,75.066887,75.096367,75.072128,75.080742,75.048790,75.067902,75.025513,75.042328,75.064262</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>74.887749,74.908646,75.055588,75.029976,75.069939,75.076935,75.084778,75.191032,74.935951,75.126106,75.092087,74.990776,75.077820,75.091393,75.164215,75.159721,75.165039,75.069473,75.120461,75.091148,75.072868,75.111237,75.070480,75.111450</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>74.614464,74.557732,74.394745,74.361588,74.329079,74.324272,74.241531,74.176064,74.120804,74.003052,73.948395,73.836037,73.821869,73.667007,73.660927,73.595116,73.572113,73.573242,73.351799,73.201309,73.161057,73.036194,73.036591,72.986290</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>74.735367,74.741867,74.621521,74.586540,74.615318,74.598473,74.542267,74.486366,74.490219,74.391281,74.306519,74.334335,74.293175,74.147400,74.196617,74.164879,74.125748,74.093628,74.014534,73.908127,73.864090,73.774368,73.793190,73.752304</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>75.06426239013672</v>
+      </c>
+      <c r="G8" t="n">
+        <v>76.30999755859375</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.245735168457031</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.63246652904229</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6480930394758641</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:39</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>76.74208068847656</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>74.965546,75.018051,75.008644,75.011971,75.041710,75.068489,75.053391,75.050659,75.072365,75.069351,75.048515,75.005714,75.060776,75.060280,75.083519,75.066887,75.096367,75.072128,75.080742,75.048790,75.067902,75.025513,75.042328,75.064262</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>75.000000,74.959999,75.059998,74.820000,74.919998,75.010002,75.059998,74.889999,74.809998,74.870003,75.000000,75.430000,75.480003,75.320000,75.320000,75.279999,75.269997,75.589996,76.639999,76.690002,76.260002,76.449997,76.379997,76.309998</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.034454,0.058052,0.051354,0.191971,0.121712,0.058487,0.006607,0.160660,0.262367,0.199348,0.048515,0.424286,0.419227,0.259720,0.236481,0.213112,0.173630,0.517868,1.559257,1.641212,1.192100,1.424484,1.337669,1.245736</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.045939,0.077444,0.068417,0.256578,0.162456,0.077972,0.008802,0.214527,0.350712,0.266259,0.064687,0.562490,0.555415,0.344822,0.313968,0.283092,0.230676,0.685102,2.034522,2.140060,1.563205,1.863288,1.751335,1.632467</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6480930394758641</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>74.887749,74.908646,75.055588,75.029976,75.069939,75.076935,75.084778,75.191032,74.935951,75.126106,75.092087,74.990776,75.077820,75.091393,75.164215,75.159721,75.165039,75.069473,75.120461,75.091148,75.072868,75.111237,75.070480,75.111450</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>74.735367,74.741867,74.621521,74.586540,74.615318,74.598473,74.542267,74.486366,74.490219,74.391281,74.306519,74.334335,74.293175,74.147400,74.196617,74.164879,74.125748,74.093628,74.014534,73.908127,73.864090,73.774368,73.793190,73.752304</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:39</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>76.343117,76.389893,76.383621,76.400894,76.463043,76.462341,76.496002,76.534561,76.561951,76.560364,76.563362,76.616585,76.649025,76.645950,76.693428,76.692177,76.748947,76.709312,76.733559,76.723740,76.765747,76.750191,76.704910,76.742081</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>76.314453,76.371696,76.342392,76.401566,76.491554,76.391487,76.446304,76.571861,76.479462,76.597496,76.492737,76.488068,76.642365,76.654221,76.632294,76.777267,76.681076,76.607994,76.665749,76.693741,76.671928,76.800789,76.658310,76.614326</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>75.861870,75.748619,75.616753,75.534081,75.487427,75.418953,75.424263,75.407356,75.373924,75.216873,75.183952,75.099022,75.139984,75.051086,75.010674,74.983612,74.986969,74.918472,74.732422,74.617416,74.639221,74.553116,74.446167,74.469963</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>76.058441,76.008728,75.913185,75.858925,75.853485,75.779739,75.808571,75.807259,75.816444,75.705109,75.632263,75.699860,75.729614,75.625053,75.617691,75.625244,75.647713,75.530609,75.492500,75.428345,75.412674,75.315987,75.257942,75.266212</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>76.74208068847656</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.26999664306641</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.472084045410156</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.738752838115111</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.592071196176396</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:44</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>72.87782287597656</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>76.343117,76.389893,76.383621,76.400894,76.463043,76.462341,76.496002,76.534561,76.561951,76.560364,76.563362,76.616585,76.649025,76.645950,76.693428,76.692177,76.748947,76.709312,76.733559,76.723740,76.765747,76.750191,76.704910,76.742081</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>76.250000,76.480003,76.650002,76.400002,76.239998,76.410004,76.540001,76.449997,76.779999,76.830002,75.389999,75.199997,75.879997,75.830002,75.529999,75.930000,75.910004,75.550003,74.000000,74.129997,73.660004,73.129997,73.300003,73.269997</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.093117,0.090110,0.266381,0.000892,0.223045,0.052337,0.043999,0.084564,0.218048,0.269638,1.173363,1.416588,0.769028,0.815948,1.163429,0.762177,0.838943,1.159309,2.733559,2.593743,3.105743,3.620194,3.404907,3.472084</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.122121,0.117822,0.347528,0.001168,0.292557,0.068495,0.057485,0.110614,0.283990,0.350954,1.556390,1.883761,1.013479,1.076023,1.540354,1.003789,1.105182,1.534492,3.693999,3.498911,4.216323,4.950354,4.645166,4.738753</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.592071196176396</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>76.314453,76.371696,76.342392,76.401566,76.491554,76.391487,76.446304,76.571861,76.479462,76.597496,76.492737,76.488068,76.642365,76.654221,76.632294,76.777267,76.681076,76.607994,76.665749,76.693741,76.671928,76.800789,76.658310,76.614326</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>76.058441,76.008728,75.913185,75.858925,75.853485,75.779739,75.808571,75.807259,75.816444,75.705109,75.632263,75.699860,75.729614,75.625053,75.617691,75.625244,75.647713,75.530609,75.492500,75.428345,75.412674,75.315987,75.257942,75.266212</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:44</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>73.209755,73.144691,73.115471,73.053879,73.033287,73.020836,73.036636,73.003830,72.962593,72.998375,73.006355,72.980431,72.991760,73.019165,73.014473,72.995911,72.924286,72.939774,72.911507,72.925102,72.861656,72.920708,72.859756,72.877823</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>73.254707,73.162140,73.077431,73.108597,73.066139,73.091400,73.095444,72.963730,73.097794,73.110886,73.032860,73.140778,73.048218,73.097824,73.049835,73.067085,73.045006,72.973816,72.977394,73.056816,72.981201,72.861923,72.917892,72.967804</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>72.485100,72.220650,72.006424,71.791077,71.611969,71.496277,71.455643,71.307457,71.191216,71.124481,71.063461,70.912270,70.859795,70.732407,70.702629,70.555367,70.427345,70.334572,70.080544,70.013359,69.854134,69.833107,69.806900,69.750572</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>72.776840,72.585228,72.399506,72.307503,72.139961,72.073967,72.031525,71.946777,71.912010,71.856255,71.746384,71.774956,71.698357,71.621880,71.632401,71.496696,71.403976,71.297180,71.224632,71.216248,71.042648,71.093590,71.008133,71.010284</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>72.87782287597656</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.36000061035156</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.482177734375</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6572760773763702</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7136475473244925</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:43</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>73.51924133300781</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>73.209755,73.144691,73.115471,73.053879,73.033287,73.020836,73.036636,73.003830,72.962593,72.998375,73.006355,72.980431,72.991760,73.019165,73.014473,72.995911,72.924286,72.939774,72.911507,72.925102,72.861656,72.920708,72.859756,72.877823</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>73.139999,73.190002,73.370003,73.209999,73.269997,73.190002,73.080002,73.120003,73.300003,72.620003,73.309998,74.269997,74.349998,73.760002,73.790001,74.230003,73.940002,74.040001,73.339996,73.209999,73.690002,73.180000,73.589996,73.360001</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.069756,0.045311,0.254532,0.156120,0.236710,0.169166,0.043366,0.116173,0.337410,0.378372,0.303643,1.289566,1.358238,0.740837,0.775528,1.234092,1.015716,1.100227,0.428489,0.284897,0.828346,0.259292,0.730240,0.482178</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.095373,0.061909,0.346915,0.213250,0.323065,0.231133,0.059340,0.158880,0.460314,0.521030,0.414190,1.736321,1.826817,1.004389,1.050993,1.662525,1.373704,1.485990,0.584251,0.389151,1.124096,0.354321,0.992309,0.657276</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7136475473244925</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>73.254707,73.162140,73.077431,73.108597,73.066139,73.091400,73.095444,72.963730,73.097794,73.110886,73.032860,73.140778,73.048218,73.097824,73.049835,73.067085,73.045006,72.973816,72.977394,73.056816,72.981201,72.861923,72.917892,72.967804</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>72.776840,72.585228,72.399506,72.307503,72.139961,72.073967,72.031525,71.946777,71.912010,71.856255,71.746384,71.774956,71.698357,71.621880,71.632401,71.496696,71.403976,71.297180,71.224632,71.216248,71.042648,71.093590,71.008133,71.010284</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:43</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>73.313889,73.326302,73.316551,73.331238,73.354523,73.372070,73.381828,73.374702,73.413116,73.414268,73.398209,73.411255,73.440735,73.473953,73.481735,73.515244,73.516937,73.469635,73.492050,73.505508,73.501694,73.504379,73.515221,73.519241</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>73.369102,73.366524,73.314804,73.374718,73.365440,73.424767,73.424240,73.367500,73.507607,73.406883,73.490318,73.425362,73.571648,73.497490,73.492310,73.511620,73.501961,73.486046,73.573364,73.456291,73.456047,73.364700,73.529373,73.482132</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>72.688667,72.587288,72.450233,72.433319,72.325790,72.267601,72.277855,72.124992,72.101990,72.012733,71.972290,71.937935,71.860229,71.793282,71.743607,71.695717,71.620338,71.520805,71.355232,71.271881,71.218086,71.180374,71.141541,71.053177</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>72.924316,72.845146,72.722336,72.742012,72.711945,72.694427,72.661110,72.589111,72.641518,72.567650,72.472038,72.540436,72.474541,72.440323,72.441513,72.398918,72.334137,72.186790,72.202797,72.187759,72.096016,72.092171,72.037804,71.989090</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>73.51924133300781</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.76999664306641</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2507553100585938</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.339915035203085</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5378766274791131</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>73.941162109375</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>73.313889,73.326302,73.316551,73.331238,73.354523,73.372070,73.381828,73.374702,73.413116,73.414268,73.398209,73.411255,73.440735,73.473953,73.481735,73.515244,73.516937,73.469635,73.492050,73.505508,73.501694,73.504379,73.515221,73.519241</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>73.349998,73.589996,73.980003,74.160004,73.849998,74.050003,73.820000,73.870003,73.419998,73.629997,73.180000,73.040001,73.180000,73.779999,74.139999,72.669998,72.550003,73.070000,73.559998,73.550003,73.199997,73.930000,73.769997,73.769997</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.036109,0.263694,0.663452,0.828766,0.495475,0.677933,0.438172,0.495301,0.006882,0.215729,0.218209,0.371254,0.260735,0.306046,0.658264,0.845246,0.966934,0.399635,0.067948,0.044495,0.301697,0.425621,0.254776,0.250756</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.049229,0.358329,0.896800,1.117537,0.670921,0.915507,0.593568,0.670503,0.009374,0.292991,0.298181,0.508289,0.356292,0.414809,0.887867,1.163129,1.332783,0.546921,0.092370,0.060496,0.412154,0.575709,0.345365,0.339915</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5378766274791131</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>73.369102,73.366524,73.314804,73.374718,73.365440,73.424767,73.424240,73.367500,73.507607,73.406883,73.490318,73.425362,73.571648,73.497490,73.492310,73.511620,73.501961,73.486046,73.573364,73.456291,73.456047,73.364700,73.529373,73.482132</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>72.924316,72.845146,72.722336,72.742012,72.711945,72.694427,72.661110,72.589111,72.641518,72.567650,72.472038,72.540436,72.474541,72.440323,72.441513,72.398918,72.334137,72.186790,72.202797,72.187759,72.096016,72.092171,72.037804,71.989090</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>73.742188,73.777763,73.772491,73.808205,73.838570,73.864769,73.851814,73.861000,73.884338,73.872932,73.837257,73.844910,73.871277,73.875992,73.861938,73.899971,73.926102,73.903015,73.929832,73.902412,73.909386,73.907402,73.922569,73.941162</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>73.751709,73.724838,73.808594,73.841812,73.847473,73.776726,73.903107,73.881332,73.901611,73.818504,73.863541,73.845917,73.908684,73.849167,73.873474,73.884254,73.898293,73.885185,73.902046,73.864372,73.885567,73.860161,73.898270,73.889641</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>73.074837,72.995163,72.856911,72.838890,72.745003,72.685272,72.648468,72.525818,72.492531,72.378845,72.286888,72.247742,72.200722,72.112373,72.000961,71.965569,71.906906,71.840782,71.714119,71.583778,71.569061,71.506554,71.495079,71.440292</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>73.326965,73.265480,73.170990,73.181282,73.155174,73.123779,73.071045,73.002480,73.039223,72.927063,72.828148,72.887108,72.840729,72.766190,72.752197,72.705482,72.654976,72.554390,72.582512,72.517662,72.466728,72.422882,72.419441,72.395241</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>73.941162109375</v>
+      </c>
+      <c r="G12" t="n">
+        <v>74.08000183105469</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1388397216796875</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1874186261446409</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6116344471985222</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:53</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n">
+        <v>74.02084350585938</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>73.742188,73.777763,73.772491,73.808205,73.838570,73.864769,73.851814,73.861000,73.884338,73.872932,73.837257,73.844910,73.871277,73.875992,73.861938,73.899971,73.926102,73.903015,73.929832,73.902412,73.909386,73.907402,73.922569,73.941162</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>73.610001,73.419998,73.599998,73.430000,73.320000,73.709999,73.940002,73.800003,74.120003,74.309998,74.599998,74.540001,74.570000,74.519997,74.690002,74.449997,74.730003,74.419998,74.419998,74.690002,74.440002,74.430000,74.330002,74.080002</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.132187,0.357765,0.172493,0.378205,0.518570,0.154770,0.088188,0.060997,0.235665,0.437066,0.762741,0.695091,0.698723,0.644005,0.828064,0.550026,0.803901,0.516983,0.490166,0.787590,0.530616,0.522598,0.407433,0.138840</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.179578,0.487285,0.234365,0.515055,0.707270,0.209971,0.119270,0.082652,0.317950,0.588165,1.022442,0.932507,0.937002,0.864204,1.108668,0.738786,1.075741,0.694683,0.658648,1.054479,0.712811,0.702134,0.548140,0.187419</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6116344471985222</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>73.751709,73.724838,73.808594,73.841812,73.847473,73.776726,73.903107,73.881332,73.901611,73.818504,73.863541,73.845917,73.908684,73.849167,73.873474,73.884254,73.898293,73.885185,73.902046,73.864372,73.885567,73.860161,73.898270,73.889641</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>73.326965,73.265480,73.170990,73.181282,73.155174,73.123779,73.071045,73.002480,73.039223,72.927063,72.828148,72.887108,72.840729,72.766190,72.752197,72.705482,72.654976,72.554390,72.582512,72.517662,72.466728,72.422882,72.419441,72.395241</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:53</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>74.060638,74.059715,74.053566,74.045120,74.079689,74.065681,74.075333,74.093262,74.082817,74.072220,74.048592,74.060066,74.069901,74.063461,74.048126,74.061333,74.035316,74.018539,74.055687,74.034416,74.007530,74.007568,73.983086,74.020844</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>74.031609,74.052589,74.056519,74.069038,74.111565,74.041550,74.101158,74.097755,74.102951,74.099113,74.088753,74.077797,74.109138,74.071854,74.084435,74.114120,74.058632,74.014122,74.029152,74.077156,74.012489,74.006157,74.038300,73.979424</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>73.645363,73.517578,73.399384,73.331230,73.237038,73.162407,73.095093,73.001198,72.927444,72.858223,72.811378,72.743446,72.707016,72.625687,72.535378,72.441383,72.360542,72.296120,72.200485,72.111900,72.047539,71.990364,71.937737,71.902534</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>73.806450,73.727577,73.638138,73.596649,73.570274,73.486786,73.452255,73.409271,73.389145,73.293907,73.246498,73.266663,73.242104,73.155304,73.125710,73.045280,73.003120,72.886734,72.934616,72.848389,72.787689,72.751770,72.711731,72.705429</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>74.02084350585938</v>
+      </c>
+      <c r="G13" t="n">
+        <v>72.84999847412109</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.170845031738281</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.607199802693486</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.127069426811524</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>72.74435424804688</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>74.060638,74.059715,74.053566,74.045120,74.079689,74.065681,74.075333,74.093262,74.082817,74.072220,74.048592,74.060066,74.069901,74.063461,74.048126,74.061333,74.035316,74.018539,74.055687,74.034416,74.007530,74.007568,73.983086,74.020844</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>73.750000,74.169998,74.029999,73.599998,73.580002,73.419998,73.480003,73.489998,73.550003,73.199997,72.949997,73.000000,73.250000,73.279999,73.019997,73.000000,72.889999,72.650002,72.769997,72.790001,72.949997,72.980003,73.010002,72.849998</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.310638,0.110283,0.023567,0.445122,0.499687,0.645683,0.595330,0.603264,0.532814,0.872223,1.098595,1.060066,0.819901,0.783462,1.028129,1.061333,1.145317,1.368537,1.285690,1.244415,1.057533,1.027565,0.973084,1.170846</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.421204,0.148690,0.031835,0.604785,0.679107,0.879437,0.810193,0.820879,0.724424,1.191562,1.505956,1.452145,1.119319,1.069135,1.408011,1.453881,1.571295,1.883740,1.766786,1.709596,1.449668,1.408008,1.332809,1.607200</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.127069426811524</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>74.031609,74.052589,74.056519,74.069038,74.111565,74.041550,74.101158,74.097755,74.102951,74.099113,74.088753,74.077797,74.109138,74.071854,74.084435,74.114120,74.058632,74.014122,74.029152,74.077156,74.012489,74.006157,74.038300,73.979424</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>73.806450,73.727577,73.638138,73.596649,73.570274,73.486786,73.452255,73.409271,73.389145,73.293907,73.246498,73.266663,73.242104,73.155304,73.125710,73.045280,73.003120,72.886734,72.934616,72.848389,72.787689,72.751770,72.711731,72.705429</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>72.861984,72.848930,72.829605,72.792999,72.830994,72.834534,72.816917,72.850731,72.825348,72.846397,72.836609,72.813232,72.813759,72.813805,72.792671,72.783958,72.739029,72.758858,72.754059,72.754166,72.753983,72.740517,72.716972,72.744354</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>72.860611,72.854469,72.846886,72.856850,72.865967,72.801308,72.861778,72.866325,72.885674,72.879013,72.878448,72.897278,72.907120,72.912682,72.868523,72.802101,72.908546,72.864967,72.830605,72.867432,72.845375,72.798599,72.773842,72.862892</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>72.509384,72.379860,72.215958,72.112823,72.072647,72.002075,71.894142,71.819641,71.727997,71.668869,71.647232,71.528412,71.490746,71.389580,71.361107,71.258995,71.127182,71.109680,70.996574,70.972977,70.938683,70.867043,70.846024,70.784683</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>72.594719,72.557671,72.433662,72.343826,72.333885,72.305466,72.267899,72.217278,72.169060,72.080696,72.009468,72.052536,71.987411,71.892723,71.937469,71.832207,71.720833,71.666969,71.684196,71.634521,71.615829,71.600456,71.577271,71.534264</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>72.74435424804688</v>
+      </c>
+      <c r="G14" t="n">
+        <v>73.12000274658203</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3756484985351562</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5137424568172843</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6456584599314109</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:51</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>73.36207580566406</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>72.861984,72.848930,72.829605,72.792999,72.830994,72.834534,72.816917,72.850731,72.825348,72.846397,72.836609,72.813232,72.813759,72.813805,72.792671,72.783958,72.739029,72.758858,72.754059,72.754166,72.753983,72.740517,72.716972,72.744354</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>73.089996,72.879997,72.930000,72.900002,72.970001,72.769997,72.769997,72.830002,72.860001,72.910004,72.970001,72.730003,72.629997,71.870003,71.029999,71.199997,71.489998,71.800003,71.849998,71.879997,72.040001,72.559998,73.059998,73.120003</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.228012,0.031067,0.100395,0.107003,0.139007,0.064537,0.046920,0.020729,0.034653,0.063607,0.133392,0.083229,0.183762,0.943802,1.762672,1.583961,1.249031,0.958855,0.904061,0.874169,0.713982,0.180519,0.343026,0.375649</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.311961,0.042628,0.137660,0.146780,0.190499,0.088687,0.064478,0.028462,0.047561,0.087240,0.182804,0.114435,0.253011,1.313207,2.481588,2.224664,1.747141,1.335453,1.258261,1.216150,0.991091,0.248786,0.469512,0.513743</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6456584599314109</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>72.860611,72.854469,72.846886,72.856850,72.865967,72.801308,72.861778,72.866325,72.885674,72.879013,72.878448,72.897278,72.907120,72.912682,72.868523,72.802101,72.908546,72.864967,72.830605,72.867432,72.845375,72.798599,72.773842,72.862892</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>72.594719,72.557671,72.433662,72.343826,72.333885,72.305466,72.267899,72.217278,72.169060,72.080696,72.009468,72.052536,71.987411,71.892723,71.937469,71.832207,71.720833,71.666969,71.684196,71.634521,71.615829,71.600456,71.577271,71.534264</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:51</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>73.078079,73.112267,73.134384,73.133713,73.199081,73.203728,73.216461,73.270905,73.259529,73.272415,73.302498,73.284454,73.292381,73.290527,73.257980,73.243340,73.235268,73.254745,73.256447,73.283569,73.291908,73.310577,73.316208,73.362076</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>73.062325,73.062851,73.141800,73.128960,73.228058,73.216881,73.243416,73.265778,73.309258,73.252068,73.325394,73.369545,73.344658,73.338081,73.309677,73.347267,73.330994,73.325333,73.330978,73.352821,73.252365,73.343338,73.382759,73.393524</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>72.546005,72.461845,72.335022,72.262665,72.241722,72.183472,72.095909,72.083420,71.975670,71.884224,71.858887,71.785789,71.743950,71.678467,71.589760,71.557144,71.453560,71.464188,71.295708,71.299446,71.230743,71.230736,71.210609,71.172791</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>72.745834,72.723091,72.622948,72.589340,72.608192,72.563202,72.534233,72.533943,72.513245,72.426483,72.363457,72.390846,72.338402,72.268883,72.257355,72.226959,72.123474,72.111740,72.078667,72.078789,72.007149,72.028801,72.011826,72.036942</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>73.36207580566406</v>
+      </c>
+      <c r="G15" t="n">
+        <v>72.87999725341797</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4820785522460938</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6614689495250837</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3983200651664827</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>72.87436676025391</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>73.078079,73.112267,73.134384,73.133713,73.199081,73.203728,73.216461,73.270905,73.259529,73.272415,73.302498,73.284454,73.292381,73.290527,73.257980,73.243340,73.235268,73.254745,73.256447,73.283569,73.291908,73.310577,73.316208,73.362076</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>73.449997,73.529999,73.379997,73.400002,73.120003,73.309998,73.209999,72.940002,72.879997,72.900002,73.029999,72.970001,73.080002,73.250000,73.489998,73.650002,73.599998,73.910004,73.570000,73.540001,73.160004,72.930000,72.949997,72.879997</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.371918,0.417732,0.245613,0.266289,0.079078,0.106270,0.006462,0.330903,0.379532,0.372413,0.272499,0.314453,0.212379,0.040527,0.232018,0.406662,0.364730,0.655259,0.313553,0.256432,0.131904,0.380577,0.366211,0.482079</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.506355,0.568111,0.334714,0.362791,0.108149,0.144959,0.008827,0.453664,0.520763,0.510855,0.373133,0.430934,0.290612,0.055327,0.315714,0.552154,0.495558,0.886563,0.426196,0.348697,0.180296,0.521838,0.502003,0.661469</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3983200651664827</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>73.062325,73.062851,73.141800,73.128960,73.228058,73.216881,73.243416,73.265778,73.309258,73.252068,73.325394,73.369545,73.344658,73.338081,73.309677,73.347267,73.330994,73.325333,73.330978,73.352821,73.252365,73.343338,73.382759,73.393524</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>72.745834,72.723091,72.622948,72.589340,72.608192,72.563202,72.534233,72.533943,72.513245,72.426483,72.363457,72.390846,72.338402,72.268883,72.257355,72.226959,72.123474,72.111740,72.078667,72.078789,72.007149,72.028801,72.011826,72.036942</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>72.851700,72.843155,72.827667,72.801682,72.815483,72.814987,72.804047,72.814713,72.819122,72.828323,72.840874,72.838905,72.852806,72.889427,72.877281,72.885727,72.882065,72.888466,72.897820,72.904732,72.868073,72.902649,72.885719,72.874367</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>72.840492,72.811401,72.797646,72.781891,72.854332,72.802681,72.792221,72.816368,72.916977,72.812332,72.884583,72.897148,72.939911,72.888283,72.916512,73.015724,72.942070,72.953491,72.862885,72.988922,72.928665,72.906631,72.872902,72.846169</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>72.486763,72.385376,72.246872,72.149216,72.057869,72.000351,71.933983,71.848991,71.764320,71.682243,71.626640,71.586662,71.577316,71.553299,71.468987,71.394150,71.315475,71.273003,71.152702,71.123398,71.038483,71.027893,70.983887,70.900406</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>72.629898,72.562546,72.457512,72.383530,72.346886,72.308693,72.246269,72.203568,72.205788,72.105186,72.050232,72.089119,72.053635,72.031944,72.018547,71.960480,71.921989,71.850174,71.877945,71.826820,71.723763,71.761169,71.715927,71.663429</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>72.87436676025391</v>
+      </c>
+      <c r="G16" t="n">
+        <v>73.44999694824219</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5756301879882812</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7837034879578131</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7479087028551353</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>73.31657409667969</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>72.851700,72.843155,72.827667,72.801682,72.815483,72.814987,72.804047,72.814713,72.819122,72.828323,72.840874,72.838905,72.852806,72.889427,72.877281,72.885727,72.882065,72.888466,72.897820,72.904732,72.868073,72.902649,72.885719,72.874367</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>72.769997,72.839996,72.510002,72.430000,72.269997,72.650002,72.529999,72.360001,72.330002,73.180000,73.699997,73.540001,73.339996,73.620003,73.900002,73.949997,73.809998,73.650002,73.480003,73.489998,73.000000,73.680000,73.800003,73.449997</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.081703,0.003159,0.317665,0.371682,0.545486,0.164985,0.274048,0.454712,0.489120,0.351677,0.859123,0.701096,0.487190,0.730576,1.022721,1.064270,0.927933,0.761536,0.582183,0.585266,0.131927,0.777351,0.914284,0.575630</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.112276,0.004336,0.438098,0.513160,0.754790,0.227096,0.377841,0.628403,0.676234,0.480565,1.165703,0.953353,0.664290,0.992360,1.383925,1.439175,1.257191,1.033993,0.792302,0.796388,0.180722,1.055037,1.238867,0.783703</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7479087028551353</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>72.840492,72.811401,72.797646,72.781891,72.854332,72.802681,72.792221,72.816368,72.916977,72.812332,72.884583,72.897148,72.939911,72.888283,72.916512,73.015724,72.942070,72.953491,72.862885,72.988922,72.928665,72.906631,72.872902,72.846169</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>72.629898,72.562546,72.457512,72.383530,72.346886,72.308693,72.246269,72.203568,72.205788,72.105186,72.050232,72.089119,72.053635,72.031944,72.018547,71.960480,71.921989,71.850174,71.877945,71.826820,71.723763,71.761169,71.715927,71.663429</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>73.377182,73.369736,73.344543,73.330353,73.342636,73.340591,73.325752,73.337990,73.360359,73.338394,73.370972,73.370140,73.352814,73.375603,73.357742,73.351959,73.348160,73.339104,73.340332,73.317825,73.293083,73.321732,73.332314,73.316574</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>73.363808,73.382179,73.289268,73.339386,73.303490,73.274040,73.283974,73.337936,73.375648,73.348450,73.383202,73.344704,73.348900,73.330055,73.393692,73.420044,73.409241,73.376747,73.297371,73.392448,73.335236,73.375351,73.300095,73.247704</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>72.919418,72.791916,72.639610,72.555969,72.458038,72.398003,72.303703,72.247276,72.204926,72.118851,72.090981,72.046272,72.013039,72.002586,71.890717,71.815277,71.744072,71.716599,71.594902,71.535469,71.481667,71.467232,71.442619,71.415260</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>73.099564,73.030930,72.904449,72.851959,72.783615,72.725052,72.658989,72.638069,72.663605,72.562271,72.532852,72.564865,72.515579,72.500046,72.447952,72.412537,72.385689,72.302132,72.319763,72.233955,72.181129,72.170555,72.170975,72.128372</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>73.31657409667969</v>
+      </c>
+      <c r="G17" t="n">
+        <v>73.77999877929688</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4634246826171875</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6281169562003671</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5760799942280604</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>73.78899383544922</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>73.377182,73.369736,73.344543,73.330353,73.342636,73.340591,73.325752,73.337990,73.360359,73.338394,73.370972,73.370140,73.352814,73.375603,73.357742,73.351959,73.348160,73.339104,73.340332,73.317825,73.293083,73.321732,73.332314,73.316574</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>73.760002,73.680000,73.349998,73.599998,73.279999,73.220001,73.540001,73.870003,73.750000,73.559998,73.739998,73.919998,73.660004,73.709999,74.099998,74.139999,74.209999,74.070000,74.050003,73.449997,73.449997,74.059998,74.160004,73.779999</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.382820,0.310264,0.005455,0.269645,0.062637,0.120590,0.214249,0.532013,0.389641,0.221604,0.369026,0.549858,0.307190,0.334396,0.742256,0.788040,0.861839,0.730896,0.709671,0.132172,0.156914,0.738266,0.827690,0.463425</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.519008,0.421097,0.007438,0.366366,0.085477,0.164695,0.291337,0.720201,0.528327,0.301256,0.500442,0.743856,0.417037,0.453664,1.001696,1.062909,1.161352,0.986763,0.958367,0.179948,0.213634,0.996848,1.116086,0.628117</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5760799942280604</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>73.363808,73.382179,73.289268,73.339386,73.303490,73.274040,73.283974,73.337936,73.375648,73.348450,73.383202,73.344704,73.348900,73.330055,73.393692,73.420044,73.409241,73.376747,73.297371,73.392448,73.335236,73.375351,73.300095,73.247704</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>73.099564,73.030930,72.904449,72.851959,72.783615,72.725052,72.658989,72.638069,72.663605,72.562271,72.532852,72.564865,72.515579,72.500046,72.447952,72.412537,72.385689,72.302132,72.319763,72.233955,72.181129,72.170555,72.170975,72.128372</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>73.774025,73.777885,73.773834,73.759743,73.794228,73.794640,73.800751,73.804123,73.821922,73.797195,73.844452,73.859032,73.829979,73.848595,73.833542,73.824539,73.824966,73.808083,73.826607,73.780205,73.768105,73.788551,73.794037,73.788994</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>73.779907,73.776245,73.742043,73.757301,73.698288,73.750008,73.750832,73.850037,73.850586,73.831459,73.838013,73.866013,73.780777,73.791542,73.865501,73.867279,73.820671,73.767471,73.692619,73.842178,73.796951,73.835121,73.775719,73.706978</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>73.339882,73.222549,73.126381,73.042992,72.985184,72.934067,72.869423,72.802795,72.778336,72.687386,72.661713,72.623535,72.576500,72.537666,72.437813,72.361755,72.308083,72.255325,72.129906,72.027481,72.009125,72.007126,71.966354,71.946556</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>73.502975,73.444016,73.360107,73.308731,73.274109,73.207603,73.186432,73.165321,73.194756,73.103180,73.061989,73.097267,73.040977,73.024261,72.964684,72.927658,72.919456,72.801620,72.831230,72.719002,72.711555,72.652840,72.674828,72.612167</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>73.78899383544922</v>
+      </c>
+      <c r="G18" t="n">
+        <v>73.44999694824219</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3389968872070312</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4615342427391948</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3285427307445773</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:50</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>73.42535400390625</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>73.774025,73.777885,73.773834,73.759743,73.794228,73.794640,73.800751,73.804123,73.821922,73.797195,73.844452,73.859032,73.829979,73.848595,73.833542,73.824539,73.824966,73.808083,73.826607,73.780205,73.768105,73.788551,73.794037,73.788994</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>73.730003,74.089996,73.949997,73.910004,74.019997,73.949997,73.769997,73.699997,74.000000,73.910004,73.889999,73.889999,74.209999,74.470001,74.459999,74.410004,74.320000,74.050003,73.949997,73.970001,74.010002,73.680000,73.470001,73.449997</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.044022,0.312111,0.176163,0.150261,0.225769,0.155357,0.030754,0.104126,0.178078,0.112809,0.045547,0.030967,0.380020,0.621406,0.626457,0.585465,0.495034,0.241920,0.123390,0.189796,0.241897,0.108551,0.324036,0.338997</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.059707,0.421260,0.238219,0.203302,0.305010,0.210084,0.041690,0.141284,0.240646,0.152630,0.061642,0.041910,0.512087,0.834438,0.841334,0.786809,0.666084,0.326698,0.166856,0.256585,0.326844,0.147327,0.441045,0.461534</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3285427307445773</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>73.779907,73.776245,73.742043,73.757301,73.698288,73.750008,73.750832,73.850037,73.850586,73.831459,73.838013,73.866013,73.780777,73.791542,73.865501,73.867279,73.820671,73.767471,73.692619,73.842178,73.796951,73.835121,73.775719,73.706978</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>73.502975,73.444016,73.360107,73.308731,73.274109,73.207603,73.186432,73.165321,73.194756,73.103180,73.061989,73.097267,73.040977,73.024261,72.964684,72.927658,72.919456,72.801620,72.831230,72.719002,72.711555,72.652840,72.674828,72.612167</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:50</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>73.449547,73.452492,73.437035,73.408882,73.403008,73.388031,73.371773,73.367554,73.370918,73.377312,73.402100,73.379410,73.400421,73.438263,73.440468,73.443779,73.450493,73.460785,73.488708,73.456520,73.440063,73.443939,73.431656,73.425354</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>73.448318,73.486366,73.426849,73.429680,73.370056,73.431595,73.361313,73.422089,73.435905,73.407402,73.420174,73.452629,73.408920,73.416565,73.455414,73.478615,73.472015,73.488632,73.460846,73.516899,73.464325,73.463753,73.434654,73.406265</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>73.157570,73.052345,72.926132,72.825966,72.731697,72.650093,72.571510,72.457466,72.436562,72.378654,72.356033,72.272484,72.283173,72.266556,72.206757,72.125740,72.085663,72.065262,71.953697,71.891357,71.843788,71.809044,71.771530,71.731247</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>73.231682,73.194756,73.095276,73.028862,72.958694,72.902885,72.853714,72.812500,72.801941,72.721939,72.673347,72.710686,72.690117,72.677376,72.674652,72.614464,72.611252,72.523643,72.587692,72.486755,72.460709,72.427231,72.410927,72.342796</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>73.42535400390625</v>
+      </c>
+      <c r="G19" t="n">
+        <v>72.66000366210938</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.765350341796875</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.053330998104517</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6506412275476818</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="n">
+        <v>72.66754150390625</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>73.449547,73.452492,73.437035,73.408882,73.403008,73.388031,73.371773,73.367554,73.370918,73.377312,73.402100,73.379410,73.400421,73.438263,73.440468,73.443779,73.450493,73.460785,73.488708,73.456520,73.440063,73.443939,73.431656,73.425354</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>73.800003,74.150002,73.980003,73.800003,73.910004,73.220001,73.220001,73.379997,73.070000,73.169998,73.389999,73.250000,73.370003,73.120003,72.750000,72.739998,72.790001,72.800003,72.629997,72.629997,72.589996,72.669998,72.639999,72.660004</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.350456,0.697510,0.542968,0.391121,0.506996,0.168030,0.151772,0.012443,0.300918,0.207314,0.012101,0.129410,0.030418,0.318260,0.690468,0.703781,0.660492,0.660782,0.858711,0.826523,0.850067,0.773941,0.791657,0.765350</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.474873,0.940674,0.733939,0.529974,0.685964,0.229486,0.207282,0.016957,0.411822,0.283332,0.016488,0.176669,0.041459,0.435257,0.949097,0.967530,0.907394,0.907667,1.182309,1.137991,1.171052,1.065007,1.089836,1.053331</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6506412275476818</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>73.448318,73.486366,73.426849,73.429680,73.370056,73.431595,73.361313,73.422089,73.435905,73.407402,73.420174,73.452629,73.408920,73.416565,73.455414,73.478615,73.472015,73.488632,73.460846,73.516899,73.464325,73.463753,73.434654,73.406265</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>73.231682,73.194756,73.095276,73.028862,72.958694,72.902885,72.853714,72.812500,72.801941,72.721939,72.673347,72.710686,72.690117,72.677376,72.674652,72.614464,72.611252,72.523643,72.587692,72.486755,72.460709,72.427231,72.410927,72.342796</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>72.629898,72.620651,72.622078,72.582985,72.595619,72.580589,72.597664,72.574867,72.575531,72.606949,72.642509,72.599030,72.652382,72.673653,72.650269,72.633499,72.656776,72.656654,72.661942,72.686607,72.659233,72.643890,72.670120,72.667542</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>72.671669,72.679619,72.644638,72.628983,72.594986,72.618820,72.641594,72.597534,72.710320,72.644882,72.651123,72.735909,72.726509,72.719772,72.759766,72.692665,72.747169,72.788620,72.738800,72.805161,72.756454,72.647018,72.715347,72.756027</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>72.433678,72.331467,72.229919,72.113487,72.071495,71.977829,71.930946,71.785828,71.781288,71.739227,71.726173,71.595833,71.607422,71.559464,71.522949,71.444115,71.441772,71.408943,71.277237,71.294830,71.203804,71.166336,71.182167,71.140373</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>72.465912,72.439865,72.367195,72.298820,72.251526,72.200676,72.203545,72.128624,72.132278,72.068054,72.028549,72.047806,72.007034,71.968788,71.987442,71.905365,71.919235,71.842117,71.865219,71.818443,71.781731,71.740662,71.754776,71.723129</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>72.66754150390625</v>
+      </c>
+      <c r="G20" t="n">
+        <v>73.93000030517578</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.262458801269531</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.707640735909949</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.218824322836761</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="n">
+        <v>73.86324310302734</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>72.629898,72.620651,72.622078,72.582985,72.595619,72.580589,72.597664,72.574867,72.575531,72.606949,72.642509,72.599030,72.652382,72.673653,72.650269,72.633499,72.656776,72.656654,72.661942,72.686607,72.659233,72.643890,72.670120,72.667542</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>72.610001,72.809998,72.779999,72.870003,73.129997,73.570000,73.480003,73.580002,73.839996,74.080002,73.669998,73.830002,73.519997,73.370003,73.339996,73.970001,73.779999,73.690002,73.690002,73.669998,73.669998,73.849998,73.930000,73.930000</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.019897,0.189347,0.157921,0.287018,0.534378,0.989411,0.882339,1.005135,1.264465,1.473053,1.027489,1.230972,0.867615,0.696350,0.689727,1.336502,1.123223,1.033348,1.028060,0.983391,1.010765,1.206108,1.259880,1.262458</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.027403,0.260056,0.216984,0.393876,0.730724,1.344856,1.200788,1.366043,1.712440,1.988462,1.394719,1.667306,1.180107,0.949093,0.940452,1.806817,1.522395,1.402291,1.395115,1.334860,1.372017,1.633187,1.704153,1.707640</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1.218824322836761</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>72.671669,72.679619,72.644638,72.628983,72.594986,72.618820,72.641594,72.597534,72.710320,72.644882,72.651123,72.735909,72.726509,72.719772,72.759766,72.692665,72.747169,72.788620,72.738800,72.805161,72.756454,72.647018,72.715347,72.756027</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>72.465912,72.439865,72.367195,72.298820,72.251526,72.200676,72.203545,72.128624,72.132278,72.068054,72.028549,72.047806,72.007034,71.968788,71.987442,71.905365,71.919235,71.842117,71.865219,71.818443,71.781731,71.740662,71.754776,71.723129</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>73.941704,73.947220,73.963768,73.951843,73.958588,73.941422,73.956444,73.941292,73.941277,73.938232,73.979378,73.928352,73.955574,73.963257,73.908615,73.894447,73.937309,73.903412,73.921516,73.906044,73.860786,73.856644,73.870331,73.863243</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>73.927406,73.986023,73.986725,73.941231,73.843781,73.924461,73.937393,73.945168,73.987793,73.993210,73.938110,73.955872,73.979057,73.962257,73.981750,73.969093,73.885612,73.913330,73.904022,73.993416,73.885628,73.853699,73.837440,73.861778</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>73.678764,73.542328,73.451454,73.347198,73.251160,73.149200,73.093170,72.979172,73.028114,72.921844,72.963242,72.763504,72.866364,72.789284,72.699783,72.625259,72.621201,72.559570,72.425308,72.420815,72.352463,72.295021,72.302788,72.256454</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>73.747017,73.718208,73.649132,73.588432,73.514503,73.448013,73.442780,73.401932,73.407135,73.261566,73.283760,73.254906,73.265877,73.216278,73.161377,73.098618,73.142647,72.984566,73.025856,72.944061,72.900436,72.844765,72.881561,72.800049</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>73.86324310302734</v>
+      </c>
+      <c r="G21" t="n">
+        <v>75.80000305175781</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.936759948730469</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.555092177777366</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.175561707953396</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>75.61078643798828</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>73.941704,73.947220,73.963768,73.951843,73.958588,73.941422,73.956444,73.941292,73.941277,73.938232,73.979378,73.928352,73.955574,73.963257,73.908615,73.894447,73.937309,73.903412,73.921516,73.906044,73.860786,73.856644,73.870331,73.863243</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>74.790001,74.599998,74.620003,74.669998,74.779999,74.760002,74.830002,75.029999,75.550003,75.389999,75.480003,76.430000,76.330002,76.330002,76.330002,76.080002,76.089996,76.199997,76.150002,75.830002,75.980003,75.959999,75.809998,75.800003</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.848297,0.652778,0.656235,0.718155,0.821411,0.818580,0.873558,1.088707,1.608726,1.451767,1.500625,2.501648,2.374428,2.366745,2.421387,2.185555,2.152687,2.296585,2.228486,1.923958,2.119217,2.103355,1.939667,1.936760</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.134238,0.875038,0.879435,0.961772,1.098436,1.094944,1.167390,1.451029,2.129353,1.925676,1.988110,3.273124,3.110740,3.100674,3.172261,2.872706,2.829133,3.013891,2.926442,2.537199,2.789178,2.769030,2.558589,2.555092</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2.175561707953396</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>73.927406,73.986023,73.986725,73.941231,73.843781,73.924461,73.937393,73.945168,73.987793,73.993210,73.938110,73.955872,73.979057,73.962257,73.981750,73.969093,73.885612,73.913330,73.904022,73.993416,73.885628,73.853699,73.837440,73.861778</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>73.747017,73.718208,73.649132,73.588432,73.514503,73.448013,73.442780,73.401932,73.407135,73.261566,73.283760,73.254906,73.265877,73.216278,73.161377,73.098618,73.142647,72.984566,73.025856,72.944061,72.900436,72.844765,72.881561,72.800049</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>75.782394,75.785301,75.788651,75.767372,75.758965,75.739143,75.737656,75.723938,75.759697,75.753441,75.763077,75.754776,75.745842,75.741325,75.733627,75.717796,75.745239,75.703903,75.692688,75.647224,75.611565,75.636047,75.624809,75.610786</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>75.692490,75.726936,75.777802,75.769005,75.705414,75.750259,75.677498,75.825562,75.678703,75.826889,75.740845,75.699364,75.722961,75.662186,75.693481,75.763535,75.646156,75.615578,75.561562,75.677315,75.583931,75.656746,75.520279,75.544762</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>75.293602,75.143044,75.041031,74.937828,74.856003,74.765518,74.710213,74.623260,74.689545,74.596176,74.597252,74.483002,74.518097,74.453613,74.377235,74.285217,74.225914,74.154961,74.023056,73.886963,73.895676,73.854347,73.820869,73.787491</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>75.467300,75.399246,75.311310,75.271797,75.186966,75.112091,75.085213,75.052330,75.095558,74.994583,74.985970,74.985329,74.950981,74.909042,74.856400,74.804016,74.819145,74.687866,74.664032,74.545990,74.528175,74.489388,74.497627,74.419159</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>75.61078643798828</v>
+      </c>
+      <c r="G22" t="n">
+        <v>76.45999908447266</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.849212646484375</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.110662642758037</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.17337687519244</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>76.11958312988281</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>75.782394,75.785301,75.788651,75.767372,75.758965,75.739143,75.737656,75.723938,75.759697,75.753441,75.763077,75.754776,75.745842,75.741325,75.733627,75.717796,75.745239,75.703903,75.692688,75.647224,75.611565,75.636047,75.624809,75.610786</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>75.930000,75.910004,75.940002,76.349998,76.290001,76.260002,76.389999,76.320000,76.430000,76.309998,76.529999,76.959999,77.360001,77.279999,77.120003,77.150002,77.169998,77.209999,77.290001,76.769997,76.209999,76.480003,76.849998,76.459999</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.147606,0.124703,0.151351,0.582626,0.531036,0.520859,0.652343,0.596062,0.670303,0.556557,0.766922,1.205223,1.614159,1.538674,1.386376,1.432206,1.424759,1.506096,1.597313,1.122773,0.598434,0.843956,1.225189,0.849213</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.194398,0.164277,0.199304,0.763100,0.696075,0.683004,0.853964,0.781003,0.877016,0.729336,1.002119,1.566038,2.086555,1.991038,1.797686,1.856391,1.846260,1.950649,2.066649,1.462515,0.785244,1.103499,1.594261,1.110663</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1.17337687519244</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>75.692490,75.726936,75.777802,75.769005,75.705414,75.750259,75.677498,75.825562,75.678703,75.826889,75.740845,75.699364,75.722961,75.662186,75.693481,75.763535,75.646156,75.615578,75.561562,75.677315,75.583931,75.656746,75.520279,75.544762</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>75.467300,75.399246,75.311310,75.271797,75.186966,75.112091,75.085213,75.052330,75.095558,74.994583,74.985970,74.985329,74.950981,74.909042,74.856400,74.804016,74.819145,74.687866,74.664032,74.545990,74.528175,74.489388,74.497627,74.419159</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>76.410194,76.385590,76.376617,76.357559,76.351585,76.329094,76.309700,76.309395,76.313927,76.303612,76.311264,76.304817,76.322609,76.281143,76.278862,76.264565,76.291397,76.251198,76.234856,76.164482,76.155418,76.153885,76.132622,76.119583</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>76.387199,76.345154,76.347908,76.403503,76.357246,76.378067,76.277122,76.380341,76.277611,76.293320,76.324654,76.286034,76.239014,76.188919,76.192139,76.239807,76.273560,76.165817,76.134399,76.174873,76.139572,76.187714,76.054321,76.059402</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>75.883011,75.710693,75.582108,75.487160,75.392845,75.317955,75.209167,75.132141,75.150024,75.069809,75.050232,74.955101,74.978569,74.852104,74.789848,74.726234,74.665359,74.615402,74.477760,74.317627,74.344589,74.258286,74.234344,74.196854</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>76.075119,75.976410,75.870781,75.833076,75.757751,75.677666,75.629578,75.582092,75.586647,75.517197,75.469040,75.503494,75.460800,75.379738,75.348831,75.301498,75.280731,75.199776,75.146164,75.044044,75.035835,74.979744,74.962006,74.890114</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>76.11958312988281</v>
+      </c>
+      <c r="G23" t="n">
+        <v>76.01999664306641</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09958648681640625</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1310003830755092</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4057732453066534</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:59</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>75.79154968261719</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>76.410194,76.385590,76.376617,76.357559,76.351585,76.329094,76.309700,76.309395,76.313927,76.303612,76.311264,76.304817,76.322609,76.281143,76.278862,76.264565,76.291397,76.251198,76.234856,76.164482,76.155418,76.153885,76.132622,76.119583</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>76.580002,76.489998,76.809998,76.940002,76.919998,76.889999,76.519997,76.760002,76.970001,76.589996,76.250000,76.199997,75.910004,75.629997,75.900002,75.730003,76.110001,76.360001,76.239998,76.239998,75.809998,75.809998,76.019997,76.019997</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.169808,0.104408,0.433381,0.582443,0.568413,0.560905,0.210297,0.450607,0.656074,0.286384,0.061264,0.104820,0.412605,0.651146,0.378860,0.534562,0.181396,0.108803,0.005142,0.075516,0.345420,0.343887,0.112625,0.099586</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.221739,0.136499,0.564224,0.757010,0.738967,0.729491,0.274826,0.587034,0.852377,0.373919,0.080346,0.137559,0.543545,0.860962,0.499157,0.705878,0.238335,0.142486,0.006744,0.099050,0.455640,0.453618,0.148152,0.131000</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4057732453066534</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>76.387199,76.345154,76.347908,76.403503,76.357246,76.378067,76.277122,76.380341,76.277611,76.293320,76.324654,76.286034,76.239014,76.188919,76.192139,76.239807,76.273560,76.165817,76.134399,76.174873,76.139572,76.187714,76.054321,76.059402</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>76.075119,75.976410,75.870781,75.833076,75.757751,75.677666,75.629578,75.582092,75.586647,75.517197,75.469040,75.503494,75.460800,75.379738,75.348831,75.301498,75.280731,75.199776,75.146164,75.044044,75.035835,74.979744,74.962006,74.890114</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:59</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>75.983734,75.970612,75.972252,75.958267,75.973129,75.941772,75.922134,75.880325,75.884521,75.861504,75.889565,75.863152,75.853760,75.847900,75.831299,75.811226,75.854454,75.825050,75.818893,75.832008,75.792191,75.812775,75.845207,75.791550</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>75.985977,75.988853,76.012482,75.968750,75.978790,75.993980,75.933708,75.939308,75.891998,75.885551,75.941635,75.873634,75.869347,75.812370,75.844643,75.864243,75.874535,75.741585,75.839676,75.888832,75.810219,75.841232,75.903275,75.866318</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>75.529816,75.392265,75.301453,75.229782,75.158386,75.102501,75.023117,74.885384,74.878342,74.789024,74.769341,74.747169,74.703110,74.618095,74.576866,74.497498,74.447784,74.444199,74.310341,74.297806,74.269905,74.233925,74.222336,74.148132</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>75.685448,75.598320,75.539703,75.496429,75.466118,75.401138,75.348625,75.241432,75.250862,75.157867,75.162964,75.196228,75.099907,75.047211,75.050941,74.985161,74.969421,74.928658,74.882378,74.894096,74.825020,74.868690,74.837311,74.733147</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>75.79154968261719</v>
+      </c>
+      <c r="G24" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.7084503173828125</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9260788462520425</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5009941890296277</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:44</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>76.47940063476562</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>75.983734,75.970612,75.972252,75.958267,75.973129,75.941772,75.922134,75.880325,75.884521,75.861504,75.889565,75.863152,75.853760,75.847900,75.831299,75.811226,75.854454,75.825050,75.818893,75.832008,75.792191,75.812775,75.845207,75.791550</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>76.000000,76.019997,75.730003,75.739998,75.620003,75.870003,75.820000,75.889999,76.139999,75.800003,75.949997,75.139999,74.870003,74.860001,75.089996,75.199997,75.570000,75.980003,76.389999,76.349998,76.150002,76.309998,76.360001,76.500000</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.016266,0.049385,0.242249,0.218269,0.353126,0.071769,0.102134,0.009674,0.255478,0.061501,0.060432,0.723153,0.983757,0.987899,0.741303,0.611229,0.284454,0.154953,0.571106,0.517990,0.357811,0.497223,0.514794,0.708450</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.021403,0.064963,0.319885,0.288182,0.466975,0.094595,0.134706,0.012748,0.335538,0.081136,0.079568,0.962407,1.313954,1.319663,0.987219,0.812805,0.376412,0.203940,0.747619,0.678442,0.469876,0.651582,0.674167,0.926078</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5009941890296277</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>75.985977,75.988853,76.012482,75.968750,75.978790,75.993980,75.933708,75.939308,75.891998,75.885551,75.941635,75.873634,75.869347,75.812370,75.844643,75.864243,75.874535,75.741585,75.839676,75.888832,75.810219,75.841232,75.903275,75.866318</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>75.685448,75.598320,75.539703,75.496429,75.466118,75.401138,75.348625,75.241432,75.250862,75.157867,75.162964,75.196228,75.099907,75.047211,75.050941,74.985161,74.969421,74.928658,74.882378,74.894096,74.825020,74.868690,74.837311,74.733147</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:44</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>76.473305,76.503983,76.509178,76.517487,76.533516,76.523415,76.492462,76.494080,76.493973,76.478485,76.482750,76.494370,76.461205,76.458649,76.445122,76.448021,76.475494,76.447876,76.467018,76.469147,76.487961,76.466408,76.486534,76.479401</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>76.461624,76.517937,76.556824,76.532257,76.537376,76.515053,76.490471,76.556473,76.452248,76.501122,76.511566,76.471329,76.490936,76.448914,76.472466,76.511467,76.454262,76.430099,76.517319,76.457008,76.470093,76.544090,76.536659,76.474304</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>76.065201,75.974525,75.858749,75.798386,75.736603,75.658958,75.556114,75.485008,75.461571,75.337135,75.319267,75.281036,75.193092,75.125618,75.072723,75.044220,75.003044,74.991844,74.899055,74.824242,74.852547,74.770576,74.741539,74.686241</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>76.202202,76.167557,76.107262,76.074547,76.034958,75.973953,75.907692,75.862061,75.845535,75.752548,75.704742,75.761208,75.655724,75.603203,75.591972,75.577431,75.546883,75.508858,75.483604,75.461723,75.438942,75.386993,75.376122,75.325638</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>76.47940063476562</v>
+      </c>
+      <c r="G25" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.979400634765625</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.29721938379553</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.782466452872961</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>75.41851043701172</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>76.473305,76.503983,76.509178,76.517487,76.533516,76.523415,76.492462,76.494080,76.493973,76.478485,76.482750,76.494370,76.461205,76.458649,76.445122,76.448021,76.475494,76.447876,76.467018,76.469147,76.487961,76.466408,76.486534,76.479401</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>76.349998,76.220001,76.260002,75.970001,76.180000,76.110001,76.690002,76.709999,76.769997,76.580002,76.169998,75.400002,75.680000,75.610001,75.849998,75.820000,75.690002,75.860001,75.400002,75.459999,75.559998,75.550003,75.559998,75.500000</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.123307,0.283982,0.249176,0.547486,0.353516,0.413414,0.197540,0.215919,0.276024,0.101517,0.312752,1.094368,0.781205,0.848648,0.595124,0.628021,0.785492,0.587875,1.067016,1.009148,0.927963,0.916405,0.926536,0.979401</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.161502,0.372582,0.326745,0.720660,0.464053,0.543180,0.257583,0.281474,0.359546,0.132563,0.410597,1.451417,1.032247,1.122402,0.784606,0.828306,1.037775,0.774948,1.415141,1.337328,1.228115,1.212978,1.226226,1.297220</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.782466452872961</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>76.461624,76.517937,76.556824,76.532257,76.537376,76.515053,76.490471,76.556473,76.452248,76.501122,76.511566,76.471329,76.490936,76.448914,76.472466,76.511467,76.454262,76.430099,76.517319,76.457008,76.470093,76.544090,76.536659,76.474304</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>76.202202,76.167557,76.107262,76.074547,76.034958,75.973953,75.907692,75.862061,75.845535,75.752548,75.704742,75.761208,75.655724,75.603203,75.591972,75.577431,75.546883,75.508858,75.483604,75.461723,75.438942,75.386993,75.376122,75.325638</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>75.491562,75.481636,75.473373,75.466698,75.455299,75.454536,75.445541,75.461105,75.453804,75.455429,75.432426,75.437454,75.404724,75.403725,75.390213,75.396545,75.369873,75.369164,75.374535,75.391754,75.394417,75.424126,75.423477,75.418510</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>75.455772,75.487938,75.503883,75.512337,75.467979,75.446350,75.486244,75.533722,75.475006,75.473198,75.460190,75.472656,75.463089,75.411041,75.433777,75.428833,75.417725,75.399399,75.408203,75.435905,75.482040,75.471260,75.470871,75.486351</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>75.141930,75.033768,74.904976,74.831589,74.763504,74.662621,74.589111,74.543373,74.531174,74.469551,74.414375,74.382126,74.321106,74.251839,74.213730,74.178261,74.101273,74.116974,74.030014,74.002022,73.999451,73.975525,73.950867,73.903732</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>75.262428,75.187149,75.107491,75.061493,74.998650,74.951172,74.920677,74.878639,74.863396,74.820908,74.748322,74.800720,74.712158,74.653793,74.667770,74.631599,74.571632,74.564087,74.553429,74.548096,74.521797,74.518295,74.495422,74.461548</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>75.41851043701172</v>
+      </c>
+      <c r="G26" t="n">
+        <v>76.08000183105469</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6614913940429688</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8694681626216236</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8168713574408506</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:33:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>76.17266082763672</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>75.491562,75.481636,75.473373,75.466698,75.455299,75.454536,75.445541,75.461105,75.453804,75.455429,75.432426,75.437454,75.404724,75.403725,75.390213,75.396545,75.369873,75.369164,75.374535,75.391754,75.394417,75.424126,75.423477,75.418510</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>76.180000,76.050003,76.440002,76.449997,76.370003,76.139999,76.080002,75.680000,75.599998,76.059998,76.110001,76.389999,75.580002,75.510002,75.699997,75.940002,76.129997,76.150002,76.139999,76.190002,76.209999,76.000000,76.019997,76.080002</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.688438,0.568367,0.966629,0.983299,0.914704,0.685463,0.634461,0.218895,0.146194,0.604569,0.677575,0.952545,0.175278,0.106277,0.309784,0.543457,0.760124,0.780838,0.765464,0.798248,0.815582,0.575874,0.596520,0.661492</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.903700,0.747360,1.264560,1.286199,1.197726,0.900267,0.833939,0.289238,0.193379,0.794857,0.890257,1.246950,0.231910,0.140746,0.409226,0.715641,0.998456,1.025394,1.005338,1.047708,1.070177,0.757729,0.784688,0.869469</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8168713574408506</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>75.455772,75.487938,75.503883,75.512337,75.467979,75.446350,75.486244,75.533722,75.475006,75.473198,75.460190,75.472656,75.463089,75.411041,75.433777,75.428833,75.417725,75.399399,75.408203,75.435905,75.482040,75.471260,75.470871,75.486351</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>75.262428,75.187149,75.107491,75.061493,74.998650,74.951172,74.920677,74.878639,74.863396,74.820908,74.748322,74.800720,74.712158,74.653793,74.667770,74.631599,74.571632,74.564087,74.553429,74.548096,74.521797,74.518295,74.495422,74.461548</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:33:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>76.082680,76.088539,76.095200,76.083496,76.060631,76.060669,76.064186,76.091286,76.095062,76.115143,76.109856,76.120186,76.109726,76.112144,76.113342,76.120613,76.109802,76.125893,76.147537,76.167374,76.177002,76.197876,76.186089,76.172661</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>76.047211,76.093010,76.127464,76.101402,76.077072,76.054962,76.100708,76.157196,76.076157,76.085876,76.150337,76.122490,76.115463,76.092018,76.088539,76.124039,76.109535,76.084358,76.151321,76.139061,76.191223,76.226967,76.165680,76.168678</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>75.726349,75.618332,75.501015,75.433479,75.323517,75.255310,75.206764,75.190628,75.171249,75.126900,75.087715,75.077492,75.031097,75.002945,74.959114,74.927704,74.855438,74.889755,74.812004,74.818779,74.797684,74.762505,74.723373,74.669998</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>75.853249,75.799278,75.726219,75.676712,75.578064,75.545082,75.532898,75.522133,75.521561,75.463760,75.419693,75.470482,75.430367,75.383842,75.392014,75.371788,75.317352,75.319893,75.335083,75.347923,75.317467,75.294540,75.273865,75.217010</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>76.17266082763672</v>
+      </c>
+      <c r="G27" t="n">
+        <v>75.34999847412109</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.822662353515625</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.091788148871918</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.007301472893471</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:58</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="n">
+        <v>75.41220855712891</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>76.082680,76.088539,76.095200,76.083496,76.060631,76.060669,76.064186,76.091286,76.095062,76.115143,76.109856,76.120186,76.109726,76.112144,76.113342,76.120613,76.109802,76.125893,76.147537,76.167374,76.177002,76.197876,76.186089,76.172661</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>75.690002,75.769997,75.839996,75.470001,75.510002,75.790001,75.400002,75.320000,75.440002,75.379997,75.269997,75.190002,75.570000,75.400002,75.209999,74.889999,74.919998,75.070000,75.120003,75.120003,75.269997,75.269997,75.349998,75.349998</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.392678,0.318542,0.255204,0.613495,0.550629,0.270668,0.664184,0.771286,0.655060,0.735146,0.839859,0.930184,0.539726,0.712142,0.903343,1.230614,1.189804,1.055893,1.027534,1.047371,0.907005,0.927879,0.836091,0.822663</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.518797,0.420407,0.336503,0.812899,0.729213,0.357129,0.880881,1.024013,0.868319,0.975253,1.115796,1.237111,0.714207,0.944486,1.201094,1.643228,1.588099,1.406545,1.367857,1.394264,1.205003,1.232735,1.109609,1.091788</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1.007301472893471</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>76.047211,76.093010,76.127464,76.101402,76.077072,76.054962,76.100708,76.157196,76.076157,76.085876,76.150337,76.122490,76.115463,76.092018,76.088539,76.124039,76.109535,76.084358,76.151321,76.139061,76.191223,76.226967,76.165680,76.168678</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>75.853249,75.799278,75.726219,75.676712,75.578064,75.545082,75.532898,75.522133,75.521561,75.463760,75.419693,75.470482,75.430367,75.383842,75.392014,75.371788,75.317352,75.319893,75.335083,75.347923,75.317467,75.294540,75.273865,75.217010</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:58</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>75.332573,75.353706,75.346138,75.358284,75.329079,75.327248,75.314873,75.330650,75.323891,75.324326,75.326904,75.355171,75.342323,75.345802,75.350739,75.352287,75.326164,75.339264,75.356087,75.366859,75.394600,75.391479,75.391251,75.412209</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>75.363281,75.388924,75.368889,75.364204,75.367630,75.373787,75.362305,75.340103,75.376144,75.297218,75.364861,75.384079,75.390823,75.364502,75.377129,75.349426,75.359436,75.378304,75.439293,75.363083,75.432259,75.429138,75.430740,75.484062</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>74.996597,74.893364,74.783508,74.762352,74.639336,74.572037,74.537384,74.489029,74.445366,74.389038,74.376366,74.390182,74.317047,74.296875,74.281487,74.237549,74.150650,74.173386,74.092308,74.118156,74.119774,74.060295,74.039581,73.997688</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>75.118881,75.074722,74.987556,74.967751,74.866623,74.846764,74.826019,74.794266,74.786133,74.698692,74.666061,74.729172,74.692200,74.648453,74.689003,74.640892,74.586159,74.550064,74.581902,74.590591,74.593727,74.550934,74.556915,74.507729</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>75.41220855712891</v>
+      </c>
+      <c r="G28" t="n">
+        <v>75.37000274658203</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.042205810546875</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.05599815444983382</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1537838460561117</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:50:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="n">
+        <v>75.35145568847656</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>75.332573,75.353706,75.346138,75.358284,75.329079,75.327248,75.314873,75.330650,75.323891,75.324326,75.326904,75.355171,75.342323,75.345802,75.350739,75.352287,75.326164,75.339264,75.356087,75.366859,75.394600,75.391479,75.391251,75.412209</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>75.589996,75.349998,75.459999,75.279999,75.360001,75.169998,74.989998,75.160004,75.220001,75.180000,75.349998,75.480003,75.370003,75.449997,75.410004,75.580002,75.480003,75.480003,75.440002,75.550003,75.510002,75.290001,75.400002,75.370003</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.257423,0.003708,0.113861,0.078285,0.030922,0.157250,0.324875,0.170646,0.103890,0.144326,0.023094,0.124832,0.027680,0.104195,0.059265,0.227715,0.153839,0.140739,0.083915,0.183144,0.115402,0.101478,0.008751,0.042206</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.340552,0.004920,0.150889,0.103992,0.041032,0.209192,0.433225,0.227044,0.138115,0.191974,0.030650,0.165385,0.036725,0.138098,0.078590,0.301290,0.203815,0.186459,0.111235,0.242414,0.152830,0.134783,0.011605,0.055999</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1537838460561117</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>75.363281,75.388924,75.368889,75.364204,75.367630,75.373787,75.362305,75.340103,75.376144,75.297218,75.364861,75.384079,75.390823,75.364502,75.377129,75.349426,75.359436,75.378304,75.439293,75.363083,75.432259,75.429138,75.430740,75.484062</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>75.118881,75.074722,74.987556,74.967751,74.866623,74.846764,74.826019,74.794266,74.786133,74.698692,74.666061,74.729172,74.692200,74.648453,74.689003,74.640892,74.586159,74.550064,74.581902,74.590591,74.593727,74.550934,74.556915,74.507729</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:50:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>75.362801,75.377235,75.366356,75.397781,75.373436,75.354118,75.332062,75.359207,75.354805,75.356133,75.348129,75.376045,75.370644,75.392159,75.372475,75.406898,75.369278,75.369087,75.386063,75.383850,75.406212,75.369965,75.353226,75.351456</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>75.364334,75.409744,75.346748,75.405670,75.390984,75.367111,75.387413,75.384010,75.400673,75.303741,75.371582,75.375099,75.416275,75.384026,75.403221,75.385658,75.390121,75.393890,75.430725,75.344612,75.443138,75.392250,75.341850,75.374863</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>75.090759,75.025894,74.915825,74.920792,74.823639,74.746017,74.705956,74.685738,74.632637,74.568878,74.564903,74.565620,74.508003,74.496147,74.474236,74.463448,74.372208,74.375420,74.317802,74.326286,74.307419,74.214645,74.176857,74.124901</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>75.182610,75.160172,75.090187,75.081825,75.005554,74.973267,74.943726,74.940552,74.922394,74.837341,74.797241,74.857735,74.823387,74.805290,74.841080,74.827484,74.749680,74.724152,74.755203,74.724586,74.725861,74.646721,74.635246,74.572876</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>75.35145568847656</v>
+      </c>
+      <c r="G29" t="n">
+        <v>75.12000274658203</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2314529418945312</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.3081109337486844</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3776901763061216</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:32</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>75.02333831787109</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>75.362801,75.377235,75.366356,75.397781,75.373436,75.354118,75.332062,75.359207,75.354805,75.356133,75.348129,75.376045,75.370644,75.392159,75.372475,75.406898,75.369278,75.369087,75.386063,75.383850,75.406212,75.369965,75.353226,75.351456</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>75.489998,75.510002,75.370003,75.290001,75.300003,75.389999,75.389999,75.230003,75.180000,75.209999,75.150002,75.230003,75.320000,75.489998,75.480003,75.209999,75.110001,75.160004,74.949997,74.269997,74.290001,74.550003,74.550003,75.120003</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.127197,0.132767,0.003647,0.107780,0.073433,0.035881,0.057937,0.129204,0.174805,0.146134,0.198127,0.146042,0.050644,0.097839,0.107528,0.196899,0.259277,0.209083,0.436066,1.113853,1.116211,0.819962,0.803223,0.231453</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.168495,0.175827,0.004838,0.143153,0.097521,0.047594,0.076850,0.171745,0.232515,0.194301,0.263643,0.194127,0.067239,0.129605,0.142459,0.261799,0.345197,0.278184,0.581809,1.499735,1.502505,1.099882,1.077428,0.308111</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3776901763061216</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>75.364334,75.409744,75.346748,75.405670,75.390984,75.367111,75.387413,75.384010,75.400673,75.303741,75.371582,75.375099,75.416275,75.384026,75.403221,75.385658,75.390121,75.393890,75.430725,75.344612,75.443138,75.392250,75.341850,75.374863</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>75.182610,75.160172,75.090187,75.081825,75.005554,74.973267,74.943726,74.940552,74.922394,74.837341,74.797241,74.857735,74.823387,74.805290,74.841080,74.827484,74.749680,74.724152,74.755203,74.724586,74.725861,74.646721,74.635246,74.572876</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:32</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>75.141068,75.165680,75.143387,75.124374,75.093147,75.087669,75.067917,75.087074,75.040573,75.035576,75.025650,75.055756,75.067688,75.086479,75.057297,75.069939,75.035080,75.028351,75.038742,75.034584,75.057785,75.017815,74.998878,75.023338</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>75.161652,75.191986,75.142082,75.108612,75.109512,75.098289,75.110794,75.098526,75.083305,74.983063,75.030624,75.087860,75.095421,75.095894,75.102913,75.072632,75.072464,75.079346,75.105888,75.014366,75.067657,75.057602,75.059059,75.086372</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>74.741074,74.666222,74.538567,74.482864,74.385750,74.319214,74.278961,74.263168,74.178947,74.143669,74.118698,74.157501,74.134583,74.125084,74.111237,74.084641,73.970909,73.971466,73.918755,73.920906,73.925133,73.834038,73.815292,73.784142</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>74.877037,74.851616,74.759018,74.700455,74.623009,74.599457,74.574959,74.542404,74.492973,74.432632,74.401085,74.484001,74.475616,74.446411,74.491287,74.459206,74.351410,74.340919,74.345490,74.340004,74.334885,74.275887,74.267906,74.232529</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>75.02333831787109</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75.73000335693359</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.7066650390625</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9331374722536574</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8215975156283488</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:52</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="n">
+        <v>75.68496704101562</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>75.141068,75.165680,75.143387,75.124374,75.093147,75.087669,75.067917,75.087074,75.040573,75.035576,75.025650,75.055756,75.067688,75.086479,75.057297,75.069939,75.035080,75.028351,75.038742,75.034584,75.057785,75.017815,74.998878,75.023338</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>75.400002,75.430000,75.480003,75.339996,75.769997,75.709999,75.160004,75.269997,75.690002,75.620003,75.360001,75.550003,75.900002,76.040001,75.949997,75.860001,75.839996,75.739998,75.930000,75.900002,75.900002,75.980003,75.980003,75.730003</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.258934,0.264320,0.336616,0.215622,0.676850,0.622330,0.092087,0.182923,0.649429,0.584427,0.334351,0.494247,0.832314,0.953522,0.892700,0.790062,0.804916,0.711647,0.891258,0.865418,0.842217,0.962188,0.981125,0.706665</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.343413,0.350418,0.445968,0.286199,0.893295,0.821992,0.122521,0.243022,0.858012,0.772847,0.443671,0.654199,1.096592,1.253974,1.175379,1.041473,1.061335,0.939592,1.173789,1.140208,1.109640,1.266371,1.291294,0.933138</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8215975156283488</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>75.161652,75.191986,75.142082,75.108612,75.109512,75.098289,75.110794,75.098526,75.083305,74.983063,75.030624,75.087860,75.095421,75.095894,75.102913,75.072632,75.072464,75.079346,75.105888,75.014366,75.067657,75.057602,75.059059,75.086372</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>74.877037,74.851616,74.759018,74.700455,74.623009,74.599457,74.574959,74.542404,74.492973,74.432632,74.401085,74.484001,74.475616,74.446411,74.491287,74.459206,74.351410,74.340919,74.345490,74.340004,74.334885,74.275887,74.267906,74.232529</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:52</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>75.723244,75.739304,75.758789,75.777054,75.761330,75.750298,75.718933,75.741112,75.723930,75.697594,75.681641,75.704926,75.678925,75.695312,75.686043,75.706718,75.677292,75.667107,75.695419,75.705505,75.738274,75.724068,75.693893,75.684967</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>75.711739,75.772255,75.762299,75.758598,75.711609,75.714432,75.714386,75.751053,75.701073,75.677979,75.682899,75.665680,75.657463,75.654221,75.653160,75.721413,75.644371,75.668327,75.681091,75.703796,75.714218,75.774033,75.684631,75.682983</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>75.419968,75.356949,75.270576,75.236084,75.158272,75.084084,75.006287,74.996269,74.914726,74.845779,74.799576,74.816200,74.752350,74.742111,74.720970,74.678772,74.582458,74.579727,74.509705,74.489067,74.505272,74.467346,74.423729,74.396896</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>75.521378,75.500633,75.466148,75.442566,75.376289,75.330544,75.286736,75.280190,75.230949,75.147209,75.090576,75.161613,75.127907,75.099388,75.111473,75.077278,75.007523,74.976463,74.989258,74.983978,74.988823,74.949738,74.939636,74.885956</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>75.68496704101562</v>
+      </c>
+      <c r="G31" t="n">
+        <v>76.69000244140625</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.005035400390625</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.310516844954472</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9985901188668487</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:36</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>76.74508666992188</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>75.723244,75.739304,75.758789,75.777054,75.761330,75.750298,75.718933,75.741112,75.723930,75.697594,75.681641,75.704926,75.678925,75.695312,75.686043,75.706718,75.677292,75.667107,75.695419,75.705505,75.738274,75.724068,75.693893,75.684967</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>75.209999,75.430000,75.760002,75.660004,75.930000,76.019997,76.089996,75.879997,75.769997,76.250000,76.180000,76.139999,76.730003,77.139999,77.029999,76.849998,77.220001,77.129997,76.820000,76.940002,76.889999,77.019997,76.870003,76.690002</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.513245,0.309304,0.001213,0.117050,0.168670,0.269699,0.371063,0.138885,0.046067,0.552406,0.498359,0.435073,1.051078,1.444687,1.343956,1.143280,1.542709,1.462890,1.124581,1.234497,1.151725,1.295929,1.176110,1.005035</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.682416,0.410054,0.001601,0.154706,0.222139,0.354773,0.487664,0.183033,0.060798,0.724467,0.654187,0.571412,1.369840,1.872812,1.744717,1.487678,1.997810,1.896655,1.463917,1.604494,1.497887,1.682587,1.529998,1.310517</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9985901188668487</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>75.711739,75.772255,75.762299,75.758598,75.711609,75.714432,75.714386,75.751053,75.701073,75.677979,75.682899,75.665680,75.657463,75.654221,75.653160,75.721413,75.644371,75.668327,75.681091,75.703796,75.714218,75.774033,75.684631,75.682983</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>75.521378,75.500633,75.466148,75.442566,75.376289,75.330544,75.286736,75.280190,75.230949,75.147209,75.090576,75.161613,75.127907,75.099388,75.111473,75.077278,75.007523,74.976463,74.989258,74.983978,74.988823,74.949738,74.939636,74.885956</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:36</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>76.716637,76.742317,76.744316,76.752121,76.745865,76.750633,76.743126,76.735664,76.732033,76.750381,76.758179,76.784882,76.782410,76.790298,76.768425,76.789146,76.786346,76.767090,76.797607,76.761444,76.751747,76.746521,76.742920,76.745087</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>76.724541,76.724716,76.781593,76.743156,76.705093,76.709991,76.738457,76.760223,76.704773,76.708427,76.737297,76.751808,76.715309,76.718239,76.698296,76.750900,76.714920,76.703926,76.769958,76.700226,76.705666,76.767776,76.652847,76.693687</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>76.353493,76.295670,76.189781,76.124413,76.075905,76.011566,75.963264,75.915977,75.891022,75.852791,75.821129,75.799316,75.787109,75.722702,75.690750,75.671753,75.632843,75.625160,75.595329,75.503319,75.493217,75.463623,75.416885,75.393692</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>76.469604,76.448639,76.385902,76.360107,76.304001,76.265800,76.261177,76.215630,76.191917,76.158943,76.132301,76.178711,76.150993,76.106361,76.084686,76.092804,76.050095,76.032921,76.055122,76.005341,75.967964,75.946220,75.926979,75.873779</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>76.74508666992188</v>
+      </c>
+      <c r="G32" t="n">
+        <v>84.94999694824219</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.204910278320312</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9.658517449175836</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.309746713649337</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:36</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="n">
+        <v>83.44297790527344</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>76.716637,76.742317,76.744316,76.752121,76.745865,76.750633,76.743126,76.735664,76.732033,76.750381,76.758179,76.784882,76.782410,76.790298,76.768425,76.789146,76.786346,76.767090,76.797607,76.761444,76.751747,76.746521,76.742920,76.745087</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>76.750000,76.930000,76.809998,76.750000,77.010002,76.889999,77.330002,77.250000,77.309998,77.480003,78.349998,78.339996,80.800003,81.790001,81.580002,81.610001,82.279999,82.330002,83.730003,86.589996,85.730003,84.949997,84.949997,84.949997</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.033363,0.187683,0.065682,0.002121,0.264137,0.139366,0.586876,0.514336,0.577965,0.729622,1.591819,1.555114,4.017593,4.999703,4.811577,4.820855,5.493653,5.562912,6.932396,9.828552,8.978256,8.203476,8.207077,8.204910</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.043470,0.243966,0.085512,0.002764,0.342991,0.181254,0.758924,0.665807,0.747594,0.941691,2.031678,1.985083,4.972268,6.112853,5.897986,5.907186,6.676778,6.756846,8.279465,11.350679,10.472712,9.656829,9.661068,9.658517</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>4.309746713649337</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>76.724541,76.724716,76.781593,76.743156,76.705093,76.709991,76.738457,76.760223,76.704773,76.708427,76.737297,76.751808,76.715309,76.718239,76.698296,76.750900,76.714920,76.703926,76.769958,76.700226,76.705666,76.767776,76.652847,76.693687</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>76.469604,76.448639,76.385902,76.360107,76.304001,76.265800,76.261177,76.215630,76.191917,76.158943,76.132301,76.178711,76.150993,76.106361,76.084686,76.092804,76.050095,76.032921,76.055122,76.005341,75.967964,75.946220,75.926979,75.873779</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:36</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>84.887833,84.833702,84.705475,84.615433,84.483337,84.492073,84.412537,84.333527,84.284050,84.186516,84.144463,84.041267,83.941238,83.947968,83.956680,83.846931,83.800621,83.682838,83.706139,83.653870,83.617706,83.559181,83.511131,83.442978</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>84.709236,84.575829,84.665535,84.319016,84.133522,84.125114,83.897026,84.050934,83.712746,83.651260,83.679031,83.368637,83.357834,83.370453,83.396873,83.406921,83.101028,83.110085,83.097191,83.003242,82.979202,83.084793,82.918983,82.775848</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>83.518509,83.209984,82.801521,82.404175,82.119629,81.907188,81.534279,81.287102,81.246407,81.031670,80.906647,80.601433,80.718346,80.408501,80.325386,80.140518,80.027718,79.863792,79.843666,79.614418,79.642883,79.453049,79.315094,79.241989</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>84.036674,83.819885,83.499695,83.325714,83.016640,82.854744,82.664391,82.455185,82.393890,82.208054,82.096779,81.978111,81.832191,81.723412,81.655136,81.545975,81.468063,81.308922,81.325104,81.220741,81.185104,80.995453,80.884178,80.799255</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>83.44297790527344</v>
+      </c>
+      <c r="G33" t="n">
+        <v>89.19000244140625</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.747024536132812</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.443574816480519</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.2006298579458</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:56</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="n">
+        <v>88.57203674316406</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>84.887833,84.833702,84.705475,84.615433,84.483337,84.492073,84.412537,84.333527,84.284050,84.186516,84.144463,84.041267,83.941238,83.947968,83.956680,83.846931,83.800621,83.682838,83.706139,83.653870,83.617706,83.559181,83.511131,83.442978</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>84.739998,84.419998,84.779999,84.900002,85.849998,86.120003,87.430000,87.279999,87.400002,87.190002,87.000000,86.500000,86.540001,87.320000,87.709999,87.480003,86.900002,87.239998,87.559998,87.480003,87.209999,87.639999,88.230003,89.190002</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.147835,0.413704,0.074524,0.284569,1.366661,1.627930,3.017463,2.946472,3.115952,3.003486,2.855537,2.458733,2.598763,3.372032,3.753319,3.633072,3.099381,3.557160,3.853859,3.826133,3.592293,4.080818,4.718872,5.747024</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.174457,0.490054,0.087903,0.335181,1.591918,1.890304,3.451291,3.375884,3.565162,3.444760,3.282226,2.842466,3.002962,3.861695,4.279237,4.153032,3.566606,4.077441,4.401392,4.373723,4.119130,4.656342,5.348376,6.443575</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3.2006298579458</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>84.709236,84.575829,84.665535,84.319016,84.133522,84.125114,83.897026,84.050934,83.712746,83.651260,83.679031,83.368637,83.357834,83.370453,83.396873,83.406921,83.101028,83.110085,83.097191,83.003242,82.979202,83.084793,82.918983,82.775848</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>84.036674,83.819885,83.499695,83.325714,83.016640,82.854744,82.664391,82.455185,82.393890,82.208054,82.096779,81.978111,81.832191,81.723412,81.655136,81.545975,81.468063,81.308922,81.325104,81.220741,81.185104,80.995453,80.884178,80.799255</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:56</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>89.162346,89.123642,89.077446,89.032448,88.946571,88.943871,88.899139,88.820358,88.805153,88.789680,88.765350,88.771156,88.712570,88.630608,88.692795,88.655045,88.699760,88.568443,88.559593,88.595886,88.591812,88.500473,88.545807,88.572037</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>89.003075,88.913101,89.040634,88.834885,88.721909,88.750885,88.387154,88.614456,88.386986,88.357727,88.338448,88.121643,88.205879,88.179977,88.115509,88.252380,88.088745,87.888931,87.914116,87.797249,87.876801,87.813194,87.706360,87.731598</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>88.027756,87.891251,87.614044,87.323608,87.066681,86.936806,86.544975,86.271172,86.256416,86.076073,85.872742,85.575470,85.597137,85.204971,85.098740,84.974792,84.812500,84.545471,84.266998,83.996994,83.895576,83.641312,83.519447,83.577415</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>88.493179,88.404961,88.176659,88.109612,87.862465,87.715195,87.646255,87.376862,87.357483,87.248932,87.106560,87.041962,86.928665,86.672791,86.606094,86.614250,86.531448,86.342964,86.193245,86.085556,85.990143,85.790741,85.712029,85.746254</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>88.57203674316406</v>
+      </c>
+      <c r="G34" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.437965393066406</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.784454068181189</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.005242334154738</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:59</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>94.16629028320312</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>89.162346,89.123642,89.077446,89.032448,88.946571,88.943871,88.899139,88.820358,88.805153,88.789680,88.765350,88.771156,88.712570,88.630608,88.692795,88.655045,88.699760,88.568443,88.559593,88.595886,88.591812,88.500473,88.545807,88.572037</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>89.220001,89.070000,89.419998,90.389999,90.190002,90.379997,93.230003,91.660004,91.440002,90.260002,90.849998,91.070000,91.889999,91.320000,91.599998,91.760002,91.529999,90.940002,91.849998,93.570000,93.570000,93.879997,93.879997,94.010002</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.057655,0.053642,0.342552,1.357551,1.243431,1.436126,4.330864,2.839646,2.634849,1.470322,2.084648,2.298844,3.177429,2.689392,2.907203,3.104957,2.830239,2.371559,3.290405,4.974114,4.978188,5.379524,5.334190,5.437965</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.064621,0.060225,0.383082,1.501882,1.378680,1.588987,4.645355,3.098020,2.881506,1.628985,2.294605,2.524260,3.457862,2.945019,3.173803,3.383781,3.092143,2.607829,3.582369,5.315928,5.320282,5.730213,5.681924,5.784454</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3.005242334154738</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>89.003075,88.913101,89.040634,88.834885,88.721909,88.750885,88.387154,88.614456,88.386986,88.357727,88.338448,88.121643,88.205879,88.179977,88.115509,88.252380,88.088745,87.888931,87.914116,87.797249,87.876801,87.813194,87.706360,87.731598</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>88.493179,88.404961,88.176659,88.109612,87.862465,87.715195,87.646255,87.376862,87.357483,87.248932,87.106560,87.041962,86.928665,86.672791,86.606094,86.614250,86.531448,86.342964,86.193245,86.085556,85.990143,85.790741,85.712029,85.746254</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:59</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>93.949692,93.988174,94.031906,94.125969,94.044579,94.128265,94.127335,94.089081,94.143890,94.064522,94.054703,94.101959,94.046509,93.997147,94.134178,94.147278,94.254494,94.178581,94.113556,94.099472,94.057465,94.046768,94.111084,94.166290</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>93.863480,93.661484,94.062347,93.936897,93.838470,93.985451,93.577225,93.934517,93.680061,93.625397,93.610046,93.497330,93.413986,93.551788,93.594124,93.707069,93.616440,93.454308,93.469437,93.324554,93.422440,93.520508,92.987312,93.309486</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>92.848419,92.670242,92.349854,92.170135,91.817337,91.809464,91.404221,91.011032,91.009056,90.850456,90.597130,90.303558,90.394775,89.988182,89.928848,89.870163,89.807243,89.543144,89.242432,88.842407,88.771759,88.529602,88.531906,88.686951</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>93.262589,93.168602,92.945625,93.044983,92.755173,92.696823,92.602745,92.361946,92.341919,92.109665,91.984550,92.028267,91.845886,91.581131,91.584747,91.658241,91.704048,91.426819,91.363159,91.164589,91.026726,90.850922,90.987411,90.967300</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>94.16629028320312</v>
+      </c>
+      <c r="G35" t="n">
+        <v>96.06999969482422</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.903709411621094</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.981585737137934</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.020742332285637</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:52</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>95.57928466796875</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>93.949692,93.988174,94.031906,94.125969,94.044579,94.128265,94.127335,94.089081,94.143890,94.064522,94.054703,94.101959,94.046509,93.997147,94.134178,94.147278,94.254494,94.178581,94.113556,94.099472,94.057465,94.046768,94.111084,94.166290</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>95.629997,96.760002,99.099998,94.199997,94.269997,94.430000,94.070000,93.879997,92.860001,93.269997,93.820000,94.110001,93.209999,93.070000,94.290001,94.250000,94.449997,94.480003,94.430000,92.820000,93.790001,96.330002,96.330002,96.070000</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.680305,2.771828,5.068092,0.074028,0.225418,0.301735,0.057335,0.209084,1.283889,0.794525,0.234703,0.008042,0.836510,0.927147,0.155823,0.102722,0.195503,0.301422,0.316444,1.279472,0.267464,2.283234,2.218918,1.903710</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1.757090,2.864642,5.114120,0.078586,0.239119,0.319533,0.060950,0.222714,1.382608,0.851855,0.250163,0.008545,0.897447,0.996183,0.165259,0.108989,0.206991,0.319033,0.335110,1.378445,0.285173,2.370221,2.303455,1.981586</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1.020742332285637</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>93.863480,93.661484,94.062347,93.936897,93.838470,93.985451,93.577225,93.934517,93.680061,93.625397,93.610046,93.497330,93.413986,93.551788,93.594124,93.707069,93.616440,93.454308,93.469437,93.324554,93.422440,93.520508,92.987312,93.309486</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>93.262589,93.168602,92.945625,93.044983,92.755173,92.696823,92.602745,92.361946,92.341919,92.109665,91.984550,92.028267,91.845886,91.581131,91.584747,91.658241,91.704048,91.426819,91.363159,91.164589,91.026726,90.850922,90.987411,90.967300</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:52</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>95.679008,95.654282,95.635818,95.761078,95.651352,95.656509,95.640633,95.557533,95.595459,95.367844,95.407936,95.435219,95.359375,95.347206,95.516518,95.528069,95.620804,95.542389,95.654297,95.537201,95.462631,95.546555,95.615250,95.579285</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>95.500015,95.377655,95.544029,95.629715,95.473114,95.501068,95.160118,95.360489,95.274185,95.147980,95.075027,94.960388,94.813980,94.868500,95.157608,95.338318,95.254341,95.211662,95.242821,95.187912,95.165138,95.352135,95.000031,95.095886</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>94.251068,93.975464,93.539131,93.467628,93.072533,92.886269,92.693024,92.424637,92.213669,91.908302,91.634781,91.429161,91.529510,91.228378,91.081406,91.119194,91.041672,90.941238,90.782211,90.256577,90.181244,90.101791,90.080299,90.157173</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>94.783020,94.506897,94.294022,94.321404,93.994362,93.846024,93.804367,93.550835,93.551315,93.140221,92.992615,93.054001,92.900505,92.674202,92.672829,92.765030,92.801666,92.579712,92.610565,92.452667,92.260231,92.178352,92.350800,92.179649</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>95.57928466796875</v>
+      </c>
+      <c r="G36" t="n">
+        <v>94.19000244140625</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.3892822265625</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.474978437787753</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.273575154725343</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="n">
+        <v>93.93826293945312</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>95.679008,95.654282,95.635818,95.761078,95.651352,95.656509,95.640633,95.557533,95.595459,95.367844,95.407936,95.435219,95.359375,95.347206,95.516518,95.528069,95.620804,95.542389,95.654297,95.537201,95.462631,95.546555,95.615250,95.579285</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>94.879997,93.699997,92.610001,92.309998,92.230003,92.430000,93.180000,93.309998,93.620003,94.599998,94.570000,95.370003,95.040001,95.330002,95.379997,95.099998,95.279999,95.050003,95.050003,95.349998,95.599998,95.400002,95.540001,94.190002</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0.799011,1.954285,3.025817,3.451080,3.421349,3.226509,2.460633,2.247535,1.975456,0.767846,0.837936,0.065216,0.319374,0.017204,0.136521,0.428071,0.340805,0.492386,0.604294,0.187203,0.137367,0.146553,0.075249,1.389283</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.842128,2.085683,3.267269,3.738577,3.709583,3.490759,2.640731,2.408676,2.110079,0.811676,0.886049,0.068382,0.336042,0.018047,0.143134,0.450127,0.357688,0.518028,0.635764,0.196332,0.143690,0.153620,0.078762,1.474979</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1.273575154725343</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>95.500015,95.377655,95.544029,95.629715,95.473114,95.501068,95.160118,95.360489,95.274185,95.147980,95.075027,94.960388,94.813980,94.868500,95.157608,95.338318,95.254341,95.211662,95.242821,95.187912,95.165138,95.352135,95.000031,95.095886</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>94.783020,94.506897,94.294022,94.321404,93.994362,93.846024,93.804367,93.550835,93.551315,93.140221,92.992615,93.054001,92.900505,92.674202,92.672829,92.765030,92.801666,92.579712,92.610565,92.452667,92.260231,92.178352,92.350800,92.179649</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>94.130974,93.948715,93.967293,94.108566,93.971161,93.914429,93.916367,93.979179,94.024918,93.895477,93.943283,94.075317,93.975594,93.873535,93.944397,93.986252,94.024086,93.971436,93.930084,93.945457,94.057968,93.910599,93.771790,93.938263</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>94.067383,93.984421,93.857925,93.997261,94.006508,93.938980,93.579086,93.838943,93.848686,93.732841,93.875519,93.666809,93.541176,93.771637,93.696411,93.736786,93.700768,93.555008,93.603943,93.513168,93.735298,93.601379,93.487457,93.585411</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>92.937340,92.583656,92.366882,92.426125,92.094345,91.819664,91.783554,91.758636,91.515320,91.358330,91.280807,91.151283,91.045113,90.753250,90.559708,90.634018,90.510178,90.425514,90.034302,89.863495,89.957382,89.617920,89.389153,89.611931</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>93.455238,93.074699,92.974777,93.074799,92.785301,92.591995,92.596413,92.541885,92.585312,92.339729,92.212570,92.337318,92.154602,91.859596,91.879539,91.906662,91.926712,91.752724,91.547974,91.593285,91.610565,91.255226,91.238258,91.297821</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>93.93826293945312</v>
+      </c>
+      <c r="G37" t="n">
+        <v>101.4599990844727</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7.521736145019531</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7.413499125657543</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.205219049489289</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:52</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="n">
+        <v>99.91726684570312</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>94.130974,93.948715,93.967293,94.108566,93.971161,93.914429,93.916367,93.979179,94.024918,93.895477,93.943283,94.075317,93.975594,93.873535,93.944397,93.986252,94.024086,93.971436,93.930084,93.945457,94.057968,93.910599,93.771790,93.938263</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>94.589996,93.660004,94.220001,94.269997,94.540001,94.050003,93.919998,94.650002,94.680000,95.820000,96.260002,95.000000,96.080002,96.430000,96.050003,95.370003,95.910004,96.519997,96.500000,96.629997,96.629997,101.750000,101.750000,101.459999</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.459022,0.288711,0.252708,0.161431,0.568840,0.135574,0.003631,0.670823,0.655082,1.924523,2.316719,0.924683,2.104408,2.556465,2.105606,1.383751,1.885918,2.548561,2.569916,2.684540,2.572029,7.839401,7.978210,7.521736</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.485276,0.308255,0.268211,0.171243,0.601692,0.144151,0.003866,0.708740,0.691891,2.008477,2.406731,0.973351,2.190266,2.651110,2.192198,1.450929,1.966341,2.640448,2.663125,2.778164,2.661730,7.704571,7.840993,7.413499</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>2.205219049489289</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>94.067383,93.984421,93.857925,93.997261,94.006508,93.938980,93.579086,93.838943,93.848686,93.732841,93.875519,93.666809,93.541176,93.771637,93.696411,93.736786,93.700768,93.555008,93.603943,93.513168,93.735298,93.601379,93.487457,93.585411</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>93.455238,93.074699,92.974777,93.074799,92.785301,92.591995,92.596413,92.541885,92.585312,92.339729,92.212570,92.337318,92.154602,91.859596,91.879539,91.906662,91.926712,91.752724,91.547974,91.593285,91.610565,91.255226,91.238258,91.297821</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:52</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>100.815132,100.754005,100.670502,100.616417,100.427269,100.591003,100.522758,100.486282,100.471619,100.289795,100.312225,100.416382,100.266602,100.291283,100.246231,100.101654,100.154625,100.174362,100.042656,99.987381,100.023399,99.876579,99.833595,99.917267</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>100.533218,100.625839,100.624451,100.334106,100.239883,100.224495,99.925262,100.212074,100.010529,100.070793,100.081642,99.727486,99.716789,99.892548,99.864220,99.916260,99.625572,99.599525,99.552040,99.457733,99.575165,99.672508,99.202492,99.388573</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>98.249306,97.782440,97.357964,97.131859,96.609375,96.528633,96.283020,96.033539,95.877579,95.530869,95.370819,95.206062,95.354179,95.087181,94.840149,94.851776,94.800339,94.776123,94.304260,94.100700,94.069038,93.736458,93.641373,93.826950</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>99.246384,98.918343,98.642128,98.474304,98.043526,97.970512,97.817757,97.593681,97.596123,97.191757,97.104446,97.210144,97.029221,96.859520,96.766914,96.768784,96.819427,96.701279,96.442703,96.475143,96.354362,95.924500,96.041931,96.013374</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>99.91726684570312</v>
+      </c>
+      <c r="G38" t="n">
+        <v>97.04000091552734</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.877265930175781</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.965030815158814</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.784264804785868</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:18</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="n">
+        <v>96.01962280273438</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>100.815132,100.754005,100.670502,100.616417,100.427269,100.591003,100.522758,100.486282,100.471619,100.289795,100.312225,100.416382,100.266602,100.291283,100.246231,100.101654,100.154625,100.174362,100.042656,99.987381,100.023399,99.876579,99.833595,99.917267</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>100.930000,101.599998,101.300003,101.870003,100.720001,100.199997,100.370003,99.790001,99.639999,98.589996,98.589996,97.120003,98.199997,98.379997,98.209999,98.199997,98.510002,97.970001,96.660004,97.169998,97.300003,96.639999,96.639999,97.040001</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.114868,0.845993,0.629501,1.253586,0.292732,0.391006,0.152755,0.696281,0.831620,1.699799,1.722229,3.296379,2.066605,1.911286,2.036232,1.901657,1.644623,2.204361,3.382652,2.817383,2.723396,3.236580,3.193596,2.877266</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.113810,0.832671,0.621423,1.230574,0.290640,0.390226,0.152192,0.697746,0.834624,1.724109,1.746859,3.394130,2.104486,1.942758,2.073345,1.936514,1.669498,2.250036,3.499537,2.899437,2.798968,3.349110,3.304631,2.965031</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1.784264804785868</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>100.533218,100.625839,100.624451,100.334106,100.239883,100.224495,99.925262,100.212074,100.010529,100.070793,100.081642,99.727486,99.716789,99.892548,99.864220,99.916260,99.625572,99.599525,99.552040,99.457733,99.575165,99.672508,99.202492,99.388573</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>99.246384,98.918343,98.642128,98.474304,98.043526,97.970512,97.817757,97.593681,97.596123,97.191757,97.104446,97.210144,97.029221,96.859520,96.766914,96.768784,96.819427,96.701279,96.442703,96.475143,96.354362,95.924500,96.041931,96.013374</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:18</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>96.992462,96.850365,96.817963,96.845917,96.617157,96.552261,96.515701,96.400703,96.472031,96.209854,96.176453,96.308876,96.190063,96.079155,96.297684,96.175377,96.197197,96.183167,96.158791,96.036293,96.107140,95.983231,96.017715,96.019623</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>96.571274,96.756813,96.593849,96.802834,96.552475,96.458328,96.244873,95.977707,96.326477,96.037354,95.963379,95.882233,95.681343,95.786728,96.037354,95.951630,95.857269,95.828186,95.943138,95.629875,95.780167,95.690582,95.622383,95.570709</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>95.653320,95.435463,95.138420,95.065353,94.784042,94.523209,94.334435,94.120430,93.977486,93.548203,93.212891,93.285088,93.225418,92.922691,92.939766,92.850731,92.658936,92.542068,92.145821,91.879005,91.875465,91.608261,91.630768,91.646263</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>96.231995,95.972267,95.792709,95.782669,95.402496,95.236275,95.147446,94.866982,94.982880,94.548859,94.289032,94.433891,94.233284,94.016075,94.207474,94.186119,94.042282,93.895721,93.716034,93.657906,93.592613,93.220093,93.440712,93.326485</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>96.01962280273438</v>
+      </c>
+      <c r="G39" t="n">
+        <v>101.4700012207031</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.45037841796875</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.371418500443162</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.29237267442349</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="n">
+        <v>103.5279846191406</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>96.992462,96.850365,96.817963,96.845917,96.617157,96.552261,96.515701,96.400703,96.472031,96.209854,96.176453,96.308876,96.190063,96.079155,96.297684,96.175377,96.197197,96.183167,96.158791,96.036293,96.107140,95.983231,96.017715,96.019623</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>97.279999,97.040001,96.620003,97.070000,96.800003,96.930000,96.809998,96.180000,97.500000,97.019997,97.000000,96.550003,95.480003,95.940002,95.940002,96.959999,96.830002,96.800003,96.940002,98.269997,99.709999,102.099998,100.620003,101.470001</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.287537,0.189636,0.197960,0.224083,0.182846,0.377739,0.294297,0.220703,1.027969,0.810143,0.823547,0.241127,0.710060,0.139153,0.357682,0.784622,0.632805,0.616836,0.781211,2.233704,3.602859,6.116767,4.602288,5.450378</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.295576,0.195420,0.204885,0.230846,0.188891,0.389703,0.303994,0.229468,1.054327,0.835026,0.849018,0.249743,0.743674,0.145041,0.372818,0.809222,0.653521,0.637227,0.805871,2.273027,3.613338,5.990957,4.573929,5.371418</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1.29237267442349</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>96.571274,96.756813,96.593849,96.802834,96.552475,96.458328,96.244873,95.977707,96.326477,96.037354,95.963379,95.882233,95.681343,95.786728,96.037354,95.951630,95.857269,95.828186,95.943138,95.629875,95.780167,95.690582,95.622383,95.570709</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>96.231995,95.972267,95.792709,95.782669,95.402496,95.236275,95.147446,94.866982,94.982880,94.548859,94.289032,94.433891,94.233284,94.016075,94.207474,94.186119,94.042282,93.895721,93.716034,93.657906,93.592613,93.220093,93.440712,93.326485</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>104.372879,104.227440,104.388191,104.282303,104.117134,104.042915,104.192268,104.085556,104.155510,103.844620,104.092728,104.127411,104.099869,103.968231,104.170914,103.963036,104.026192,103.690285,103.799187,103.632729,103.664276,103.310577,103.422775,103.527985</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>104.221024,104.111450,104.332947,104.020332,103.905022,103.808250,103.662460,103.770485,103.737579,103.461296,103.845306,103.393219,103.400299,103.657646,103.792038,103.609619,103.253311,103.096611,103.333969,103.018799,103.047371,103.107010,103.148849,102.925262</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>102.037498,101.544281,101.358704,101.101471,100.668633,100.266312,100.259972,99.981628,99.791672,99.206924,99.208496,99.101517,99.134796,98.642952,98.677238,98.598846,98.500328,98.198624,97.981491,97.473030,97.625229,97.073746,97.232338,97.391190</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>102.918327,102.503654,102.469505,102.266556,101.881210,101.486404,101.638321,101.283005,101.411644,100.761292,100.828262,100.906158,100.743263,100.359634,100.570137,100.553101,100.407127,100.024979,99.977936,99.838890,99.748055,99.137695,99.439369,99.415314</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>103.5279846191406</v>
+      </c>
+      <c r="G40" t="n">
+        <v>106.0500030517578</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.522018432617216</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.378140839266494</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.02875327237669</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>106.7320785522461</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>104.372879,104.227440,104.388191,104.282303,104.117134,104.042915,104.192268,104.085556,104.155510,103.844620,104.092728,104.127411,104.099869,103.968231,104.170914,103.963036,104.026192,103.690285,103.799187,103.632729,103.664276,103.310577,103.422775,103.527985</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>104.389999,104.099998,103.940002,104.419998,106.089996,106.800003,107.199997,108.949997,108.199997,108.379997,109.440002,109.059998,108.769997,109.209999,109.180000,109.129997,107.879997,106.550003,106.870003,106.800003,107.250000,107.559998,106.360001,106.050003</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.017120,0.127442,0.448189,0.137695,1.972862,2.757088,3.007729,4.864441,4.044487,4.535377,5.347274,4.932587,4.670128,5.241768,5.009086,5.166961,3.853805,2.859718,3.070816,3.167274,3.585724,4.249421,2.937226,2.522018</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.016400,0.122422,0.431199,0.131867,1.859612,2.581543,2.805717,4.464838,3.737973,4.184700,4.886033,4.522819,4.293581,4.799714,4.587916,4.734685,3.572308,2.683921,2.873412,2.965612,3.343332,3.950744,2.761589,2.378140</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3.02875327237669</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>104.221024,104.111450,104.332947,104.020332,103.905022,103.808250,103.662460,103.770485,103.737579,103.461296,103.845306,103.393219,103.400299,103.657646,103.792038,103.609619,103.253311,103.096611,103.333969,103.018799,103.047371,103.107010,103.148849,102.925262</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>102.918327,102.503654,102.469505,102.266556,101.881210,101.486404,101.638321,101.283005,101.411644,100.761292,100.828262,100.906158,100.743263,100.359634,100.570137,100.553101,100.407127,100.024979,99.977936,99.838890,99.748055,99.137695,99.439369,99.415314</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>106.571953,106.409149,106.338028,106.552689,106.195099,106.419296,106.481720,106.357597,106.569359,106.370926,106.376999,106.533554,106.593971,106.443214,106.665077,106.539696,106.638565,106.508224,106.523048,106.534958,106.684151,106.491051,106.597870,106.732079</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>106.571182,106.470047,106.238007,106.465347,106.196388,106.339493,106.092758,105.958755,106.414215,105.919952,106.144188,106.094612,106.049950,106.286087,106.266281,106.059952,106.189384,105.902840,106.346008,105.880447,106.146530,106.168198,106.181946,106.121864</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>105.255127,104.933861,104.546570,104.635857,104.024025,103.964317,103.770844,103.329948,103.378929,102.899597,102.695755,102.516045,102.655426,102.244987,102.222527,102.116104,101.943626,101.719658,101.318283,100.919418,101.181763,100.694061,100.838272,101.106781</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>105.854401,105.510361,105.247894,105.441727,104.855553,104.821999,104.837997,104.393326,104.614296,104.145035,104.017662,104.077271,104.135994,103.693413,103.807129,103.888855,103.783066,103.383339,103.301468,103.281029,103.319389,102.873123,103.217628,103.182236</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>106.7320785522461</v>
+      </c>
+      <c r="G41" t="n">
+        <v>103.5899963378906</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.142082214355469</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.033190776555877</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.284203274141245</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:55</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="n">
+        <v>103.2830429077148</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>106.571953,106.409149,106.338028,106.552689,106.195099,106.419296,106.481720,106.357597,106.569359,106.370926,106.376999,106.533554,106.593971,106.443214,106.665077,106.539696,106.638565,106.508224,106.523048,106.534958,106.684151,106.491051,106.597870,106.732079</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>104.900002,105.519997,106.290001,105.290001,105.180000,104.699997,103.019997,103.379997,103.860001,103.419998,104.150002,104.150002,103.900002,104.169998,103.940002,103.870003,103.879997,104.029999,103.589996,103.589996,103.589996,103.589996,103.589996,103.589996</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1.671951,0.889152,0.048027,1.262688,1.015099,1.719299,3.461723,2.977600,2.709358,2.950928,2.226997,2.383552,2.693969,2.273216,2.725075,2.669693,2.758568,2.478225,2.933052,2.944962,3.094155,2.901055,3.007874,3.142083</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1.593853,0.842639,0.045185,1.199248,0.965106,1.642119,3.360244,2.880247,2.608664,2.853344,2.138260,2.288577,2.592848,2.182217,2.621777,2.570225,2.655533,2.382222,2.831404,2.842902,2.986924,2.800516,2.903633,3.033191</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2.284203274141245</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>106.571182,106.470047,106.238007,106.465347,106.196388,106.339493,106.092758,105.958755,106.414215,105.919952,106.144188,106.094612,106.049950,106.286087,106.266281,106.059952,106.189384,105.902840,106.346008,105.880447,106.146530,106.168198,106.181946,106.121864</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>105.854401,105.510361,105.247894,105.441727,104.855553,104.821999,104.837997,104.393326,104.614296,104.145035,104.017662,104.077271,104.135994,103.693413,103.807129,103.888855,103.783066,103.383339,103.301468,103.281029,103.319389,102.873123,103.217628,103.182236</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:55</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>103.733139,103.562775,103.501663,103.659813,103.417435,103.530342,103.594231,103.478683,103.501778,103.426254,103.316223,103.407974,103.410728,103.307014,103.431335,103.410683,103.388718,103.323112,103.305626,103.328873,103.417572,103.225914,103.156067,103.283043</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>103.704361,103.572014,103.393013,103.509705,103.569336,103.400528,103.248146,103.184097,103.448906,103.287491,103.267883,103.112778,103.121101,103.330620,103.103676,103.061775,103.072861,103.180038,103.261688,102.751160,103.010727,102.958458,102.929527,102.878326</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>102.830872,102.491493,102.032974,102.212486,101.661598,101.586609,101.713966,101.377205,101.181099,100.902016,100.601852,100.552704,100.403618,100.183197,100.249527,100.147087,99.934181,99.754501,99.329185,99.129791,99.077492,98.629913,98.507385,98.638916</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>103.296295,102.951378,102.712204,102.813370,102.301025,102.333000,102.466507,102.155243,102.125229,101.869064,101.562042,101.668495,101.615723,101.236275,101.406593,101.503586,101.201004,101.060104,100.894524,100.964439,100.793571,100.443138,100.488770,100.497787</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>103.2830429077148</v>
+      </c>
+      <c r="G42" t="n">
+        <v>105.1500015258789</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.866958618164105</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.775519344813913</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.270565266631992</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:38</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="n">
+        <v>105.0342559814453</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>103.733139,103.562775,103.501663,103.659813,103.417435,103.530342,103.594231,103.478683,103.501778,103.426254,103.316223,103.407974,103.410728,103.307014,103.431335,103.410683,103.388718,103.323112,103.305626,103.328873,103.417572,103.225914,103.156067,103.283043</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>103.750000,103.480003,103.339996,103.459999,103.510002,103.629997,103.820000,105.360001,105.019997,104.879997,104.879997,105.129997,105.370003,105.230003,105.040001,105.519997,105.610001,105.279999,105.250000,105.239998,105.070000,105.129997,105.150002,105.150002</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.016861,0.082772,0.161667,0.199814,0.092567,0.099655,0.225769,1.881318,1.518219,1.453743,1.563774,1.722023,1.959275,1.922989,1.608666,2.109314,2.221283,1.956887,1.944374,1.911125,1.652428,1.904083,1.993935,1.866959</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.016252,0.079988,0.156442,0.193132,0.089428,0.096164,0.217462,1.785609,1.445647,1.386102,1.491013,1.637994,1.859424,1.827415,1.531479,1.998971,2.103288,1.858745,1.847386,1.815968,1.572692,1.811170,1.896276,1.775519</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1.270565266631992</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>103.704361,103.572014,103.393013,103.509705,103.569336,103.400528,103.248146,103.184097,103.448906,103.287491,103.267883,103.112778,103.121101,103.330620,103.103676,103.061775,103.072861,103.180038,103.261688,102.751160,103.010727,102.958458,102.929527,102.878326</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>103.296295,102.951378,102.712204,102.813370,102.301025,102.333000,102.466507,102.155243,102.125229,101.869064,101.562042,101.668495,101.615723,101.236275,101.406593,101.503586,101.201004,101.060104,100.894524,100.964439,100.793571,100.443138,100.488770,100.497787</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:38</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>105.249756,105.058144,105.106842,105.180450,105.066727,105.082993,105.121445,105.013123,105.121346,105.014206,104.924461,105.065369,105.002594,104.936951,105.018730,105.014809,105.106346,104.934120,104.992661,104.967690,105.079887,104.844650,104.912354,105.034256</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>104.989311,104.982933,104.962379,105.090515,105.299187,104.821129,104.755928,104.856400,104.893585,104.892471,104.775513,104.726868,104.855835,105.087921,104.835999,104.847618,104.833946,104.724144,104.948471,104.535011,104.646790,104.420021,104.786621,104.614700</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>104.398949,104.134827,103.930206,104.033775,103.661301,103.381744,103.499496,103.396355,103.129677,102.833267,102.664597,102.850952,102.599045,102.473602,102.325035,102.382217,102.244774,102.153755,101.799118,101.421822,101.563583,101.097603,101.054672,101.133041</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>104.898209,104.564537,104.547356,104.575348,104.218163,104.094803,104.111481,103.973557,104.066742,103.759865,103.609314,103.722244,103.713882,103.310135,103.357132,103.451241,103.414360,103.199173,103.025482,103.001305,102.873581,102.517792,102.599274,102.709244</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>105.0342559814453</v>
+      </c>
+      <c r="G43" t="n">
+        <v>101.6399993896484</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.394256591796861</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.339488992699217</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.541759509745034</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:11</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>101.308479309082</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>105.249756,105.058144,105.106842,105.180450,105.066727,105.082993,105.121445,105.013123,105.121346,105.014206,104.924461,105.065369,105.002594,104.936951,105.018730,105.014809,105.106346,104.934120,104.992661,104.967690,105.079887,104.844650,104.912354,105.034256</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>105.419998,104.820000,104.750000,104.610001,105.110001,105.120003,106.099998,107.120003,106.739998,106.269997,106.910004,106.389999,106.680000,105.820000,104.760002,104.459999,103.790001,101.760002,102.139999,101.510002,101.440002,101.949997,101.440002,101.639999</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.170242,0.238144,0.356842,0.570449,0.043274,0.037010,0.978553,2.106880,1.618652,1.255791,1.985543,1.324630,1.677406,0.883049,0.258728,0.554810,1.316345,3.174118,2.852662,3.457688,3.639885,2.894653,3.472352,3.394257</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.161489,0.227194,0.340661,0.545311,0.041170,0.035207,0.922294,1.966841,1.516444,1.181698,1.857209,1.245070,1.572372,0.834482,0.246972,0.531122,1.268277,3.119220,2.792894,3.406253,3.588214,2.839287,3.423059,3.339489</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1.541759509745034</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>104.989311,104.982933,104.962379,105.090515,105.299187,104.821129,104.755928,104.856400,104.893585,104.892471,104.775513,104.726868,104.855835,105.087921,104.835999,104.847618,104.833946,104.724144,104.948471,104.535011,104.646790,104.420021,104.786621,104.614700</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>104.898209,104.564537,104.547356,104.575348,104.218163,104.094803,104.111481,103.973557,104.066742,103.759865,103.609314,103.722244,103.713882,103.310135,103.357132,103.451241,103.414360,103.199173,103.025482,103.001305,102.873581,102.517792,102.599274,102.709244</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:11</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>101.593285,101.499786,101.354858,101.449875,101.212822,101.289162,101.328804,101.345612,101.356110,101.309059,101.208145,101.408081,101.359383,101.195847,101.265610,101.320435,101.197083,101.083405,101.256516,101.036263,101.160751,101.123169,101.191605,101.308479</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>101.300354,101.401512,101.181152,101.593536,101.451767,101.162399,101.148163,101.063713,100.951660,101.303207,101.146568,101.402580,101.252518,101.301193,101.003853,101.140152,101.018982,101.062645,101.447975,100.625488,100.939453,100.472916,101.178970,100.983864</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>100.225845,100.066437,99.690842,99.814682,99.403633,99.230843,99.271996,99.215988,98.915634,98.621002,98.481644,98.554474,98.257202,97.942780,97.819977,97.892075,97.616531,97.497620,97.358124,96.737701,96.802467,96.620224,96.646019,96.638626</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>100.875229,100.654419,100.404419,100.523643,100.090355,100.033798,100.060959,99.976425,99.918221,99.693420,99.479561,99.622475,99.554253,99.014000,99.046471,99.187241,98.877716,98.740349,98.728249,98.503708,98.377304,98.277565,98.377937,98.474602</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>101.308479309082</v>
+      </c>
+      <c r="G44" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.441520690917997</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.353272955101684</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.958006048748116</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:59</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="n">
+        <v>103.8362884521484</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>101.593285,101.499786,101.354858,101.449875,101.212822,101.289162,101.328804,101.345612,101.356110,101.309059,101.208145,101.408081,101.359383,101.195847,101.265610,101.320435,101.197083,101.083405,101.256516,101.036263,101.160751,101.123169,101.191605,101.308479</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>102.709999,102.980003,103.230003,103.070000,103.650002,103.379997,102.750000,102.320000,103.480003,102.870003,102.820000,103.610001,104.459999,103.620003,103.720001,103.639999,103.199997,103.050003,103.169998,103.230003,103.370003,103.620003,103.750000,103.750000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1.116714,1.480217,1.875145,1.620125,2.437180,2.090835,1.421196,0.974388,2.123893,1.560944,1.611855,2.201920,3.100616,2.424156,2.454391,2.319564,2.002914,1.966598,1.913482,2.193740,2.209252,2.496834,2.558395,2.441521</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.087250,1.437383,1.816473,1.571868,2.351355,2.022476,1.383159,0.952294,2.052467,1.517394,1.567647,2.125200,2.968233,2.339467,2.366363,2.238098,1.940808,1.908392,1.854689,2.125100,2.137227,2.409606,2.465923,2.353273</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.958006048748116</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>101.300354,101.401512,101.181152,101.593536,101.451767,101.162399,101.148163,101.063713,100.951660,101.303207,101.146568,101.402580,101.252518,101.301193,101.003853,101.140152,101.018982,101.062645,101.447975,100.625488,100.939453,100.472916,101.178970,100.983864</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>100.875229,100.654419,100.404419,100.523643,100.090355,100.033798,100.060959,99.976425,99.918221,99.693420,99.479561,99.622475,99.554253,99.014000,99.046471,99.187241,98.877716,98.740349,98.728249,98.503708,98.377304,98.277565,98.377937,98.474602</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:59</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>103.776421,103.836960,103.813774,104.020523,103.899872,104.012009,104.041420,103.984688,104.033852,103.924225,103.915955,103.953522,103.875122,103.785805,103.901909,103.890160,103.884354,103.780884,103.816078,103.720352,103.745071,103.672058,103.740051,103.836288</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>103.614311,103.695145,103.844116,103.988289,104.071381,103.955627,103.832153,103.900482,103.704041,103.714661,103.788872,103.560196,103.720200,103.977760,103.730133,103.549980,103.570847,103.682411,103.935440,103.478783,103.608681,103.338943,103.597733,103.510071</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>102.658691,102.629906,102.429932,102.686661,102.418381,102.370644,102.479553,102.350838,102.121986,101.849182,101.708664,101.707314,101.497093,101.262756,101.210930,101.191338,100.935394,100.854797,100.561417,100.256248,100.221291,99.966393,100.023674,100.010010</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>103.229584,103.172264,103.043663,103.253860,102.975586,103.037643,103.103485,102.994781,103.038757,102.787201,102.599007,102.584183,102.525810,102.126129,102.209229,102.244583,102.070328,101.936096,101.815369,101.679016,101.555908,101.331772,101.472542,101.585556</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>103.8362884521484</v>
+      </c>
+      <c r="G45" t="n">
+        <v>99.84999847412109</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.986289978027301</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3.992278456629581</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.821219078844843</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:09</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="n">
+        <v>99.44907379150391</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>103.776421,103.836960,103.813774,104.020523,103.899872,104.012009,104.041420,103.984688,104.033852,103.924225,103.915955,103.953522,103.875122,103.785805,103.901909,103.890160,103.884354,103.780884,103.816078,103.720352,103.745071,103.672058,103.740051,103.836288</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>104.290001,103.360001,103.129997,102.040001,101.949997,102.349998,102.260002,101.910004,101.930000,101.970001,102.000000,100.889999,100.570000,99.580002,100.029999,100.059998,99.550003,99.620003,99.730003,99.620003,99.059998,99.889999,100.250000,99.849998</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.513580,0.476959,0.683777,1.980522,1.949875,1.662011,1.781418,2.074684,2.103852,1.954224,1.915955,3.063523,3.305122,4.205803,3.871910,3.830162,4.334351,4.160881,4.086075,4.100349,4.685073,3.782059,3.490051,3.986290</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.492454,0.461455,0.663024,1.940927,1.912580,1.623850,1.742048,2.035800,2.064016,1.916469,1.878387,3.036498,3.286390,4.223542,3.870749,3.827866,4.353944,4.176753,4.097137,4.115990,4.729531,3.786223,3.481348,3.992278</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>2.821219078844843</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>103.614311,103.695145,103.844116,103.988289,104.071381,103.955627,103.832153,103.900482,103.704041,103.714661,103.788872,103.560196,103.720200,103.977760,103.730133,103.549980,103.570847,103.682411,103.935440,103.478783,103.608681,103.338943,103.597733,103.510071</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>103.229584,103.172264,103.043663,103.253860,102.975586,103.037643,103.103485,102.994781,103.038757,102.787201,102.599007,102.584183,102.525810,102.126129,102.209229,102.244583,102.070328,101.936096,101.815369,101.679016,101.555908,101.331772,101.472542,101.585556</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:09</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>99.693672,99.706505,99.660172,99.700317,99.535995,99.590607,99.636490,99.554359,99.592415,99.616486,99.536095,99.568130,99.583824,99.535416,99.546997,99.536491,99.492035,99.402435,99.471436,99.262314,99.319237,99.439987,99.405846,99.449074</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>99.432991,99.609482,99.643356,99.719757,99.598846,99.501091,99.605164,99.468109,99.378197,99.641716,99.466309,99.448280,99.559090,99.720070,99.572044,99.375504,99.398720,99.452042,99.815193,99.347610,99.453491,99.148438,99.450066,99.453178</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>98.717018,98.572113,98.279839,98.408867,98.104668,97.849556,97.944275,97.807762,97.516876,97.341476,97.128891,97.137604,96.944855,96.786552,96.677025,96.641914,96.360489,96.292259,96.062576,95.777908,95.845093,95.875000,95.808243,95.713974</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>99.168556,99.044449,98.890152,98.917519,98.591324,98.609589,98.542686,98.407608,98.452469,98.315575,98.118835,98.058319,98.080132,97.759438,97.705338,97.701317,97.495773,97.312553,97.326004,97.152863,97.074188,97.147217,97.119247,97.167458</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>99.44907379150391</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100.5899963378906</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.140922546386719</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.13423062722287</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.6957770183874782</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:06</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="n">
+        <v>100.4024047851562</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>99.693672,99.706505,99.660172,99.700317,99.535995,99.590607,99.636490,99.554359,99.592415,99.616486,99.536095,99.568130,99.583824,99.535416,99.546997,99.536491,99.492035,99.402435,99.471436,99.262314,99.319237,99.439987,99.405846,99.449074</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>100.230003,100.050003,99.800003,98.940002,98.599998,98.169998,98.070000,97.650002,99.160004,98.889999,99.250000,98.750000,99.260002,99.489998,99.379997,99.660004,99.629997,99.510002,100.400002,99.489998,100.139999,101.050003,100.480003,100.589996</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.536331,0.343498,0.139831,0.760315,0.935997,1.420609,1.566490,1.904357,0.432411,0.726487,0.286095,0.818130,0.323822,0.045418,0.167000,0.123513,0.137962,0.107567,0.928566,0.227684,0.820762,1.610016,1.074157,1.140922</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.535101,0.343326,0.140111,0.768460,0.949287,1.447091,1.597319,1.950187,0.436074,0.734641,0.288257,0.828486,0.326236,0.045651,0.168042,0.123934,0.138475,0.108097,0.924866,0.228851,0.819615,1.593286,1.069026,1.134230</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.6957770183874782</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>99.432991,99.609482,99.643356,99.719757,99.598846,99.501091,99.605164,99.468109,99.378197,99.641716,99.466309,99.448280,99.559090,99.720070,99.572044,99.375504,99.398720,99.452042,99.815193,99.347610,99.453491,99.148438,99.450066,99.453178</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>99.168556,99.044449,98.890152,98.917519,98.591324,98.609589,98.542686,98.407608,98.452469,98.315575,98.118835,98.058319,98.080132,97.759438,97.705338,97.701317,97.495773,97.312553,97.326004,97.152863,97.074188,97.147217,97.119247,97.167458</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:06</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>100.637177,100.612350,100.613907,100.723785,100.605331,100.644875,100.690163,100.682159,100.690971,100.615387,100.558220,100.565086,100.537277,100.435814,100.523155,100.527756,100.508194,100.350067,100.459778,100.300804,100.343735,100.317398,100.258881,100.402405</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>100.467979,100.481049,100.679688,100.618065,100.626862,100.584335,100.526901,100.535690,100.421829,100.546158,100.478119,100.453072,100.401108,100.641739,100.389206,100.455391,100.337639,100.388359,100.508194,100.281494,100.238358,100.146446,100.505257,100.261948</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>99.458237,99.301300,99.040878,99.304657,98.928696,98.699295,98.808350,98.790001,98.448563,98.202148,98.053505,98.003792,97.741356,97.491440,97.497780,97.528145,97.309273,97.092422,96.826797,96.600487,96.693184,96.515076,96.428505,96.428696</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>100.038033,99.863571,99.767319,99.810539,99.496223,99.471535,99.482117,99.381660,99.416771,99.199677,99.035110,98.903389,98.870476,98.492882,98.569290,98.650108,98.411514,98.143898,98.119949,98.011887,97.972015,97.796288,97.851082,97.975914</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>100.4024047851562</v>
+      </c>
+      <c r="G47" t="n">
+        <v>103.629997253418</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.227592468261776</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.114534935641255</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.531115810906755</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:46</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="n">
+        <v>103.16796875</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>100.637177,100.612350,100.613907,100.723785,100.605331,100.644875,100.690163,100.682159,100.690971,100.615387,100.558220,100.565086,100.537277,100.435814,100.523155,100.527756,100.508194,100.350067,100.459778,100.300804,100.343735,100.317398,100.258881,100.402405</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>100.820000,100.839996,100.360001,100.589996,100.129997,100.410004,100.760002,101.650002,101.459999,104.800003,105.160004,104.550003,105.099998,105.209999,105.290001,104.930000,105.220001,104.169998,103.940002,103.480003,103.800003,103.790001,103.709999,103.629997</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.182823,0.227646,0.253906,0.133789,0.475334,0.234871,0.069839,0.967843,0.769028,4.184616,4.601784,3.984917,4.562721,4.774185,4.766846,4.402244,4.711807,3.819931,3.480224,3.179199,3.456268,3.472603,3.451118,3.227592</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.181336,0.225750,0.252996,0.133004,0.474717,0.233912,0.069312,0.952132,0.757962,3.992954,4.375983,3.811494,4.341315,4.537767,4.527349,4.195411,4.478053,3.667017,3.348301,3.072284,3.329738,3.345797,3.327662,3.114535</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2.531115810906755</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>100.467979,100.481049,100.679688,100.618065,100.626862,100.584335,100.526901,100.535690,100.421829,100.546158,100.478119,100.453072,100.401108,100.641739,100.389206,100.455391,100.337639,100.388359,100.508194,100.281494,100.238358,100.146446,100.505257,100.261948</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>100.038033,99.863571,99.767319,99.810539,99.496223,99.471535,99.482117,99.381660,99.416771,99.199677,99.035110,98.903389,98.870476,98.492882,98.569290,98.650108,98.411514,98.143898,98.119949,98.011887,97.972015,97.796288,97.851082,97.975914</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:46</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>103.746399,103.714890,103.718132,103.788719,103.679810,103.651382,103.686638,103.705017,103.704819,103.639450,103.683563,103.730026,103.701981,103.542564,103.626137,103.584831,103.505280,103.335930,103.278358,103.208527,103.208885,103.134682,103.009422,103.167969</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>103.629822,103.748146,103.709869,103.606522,103.738678,103.700096,103.678177,103.704796,103.392723,103.666199,103.604843,103.710464,103.466187,103.820854,103.547554,103.382156,103.345665,103.125893,103.260559,103.073013,103.187263,103.044945,103.165329,102.993248</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>102.493164,102.465744,102.280029,102.486992,102.140984,101.863373,101.892197,101.807182,101.540596,101.305367,101.230576,101.113617,100.963997,100.558960,100.576393,100.457130,100.224045,99.944710,99.565735,99.396744,99.360474,99.127228,99.000809,99.021767</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>103.109024,102.985703,102.923149,102.978210,102.681396,102.549118,102.523918,102.406754,102.424149,102.242859,102.161110,102.055565,101.943710,101.554657,101.631790,101.609299,101.405502,101.089737,100.927567,100.876282,100.769051,100.463089,100.486343,100.657516</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>103.16796875</v>
+      </c>
+      <c r="G48" t="n">
+        <v>101.8300018310547</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.337966918945312</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.31392212008905</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.328303822680022</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:43</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="n">
+        <v>101.5580596923828</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>103.746399,103.714890,103.718132,103.788719,103.679810,103.651382,103.686638,103.705017,103.704819,103.639450,103.683563,103.730026,103.701981,103.542564,103.626137,103.584831,103.505280,103.335930,103.278358,103.208527,103.208885,103.134682,103.009422,103.167969</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>103.699997,103.620003,103.599998,104.370003,104.040001,104.139999,104.080002,101.580002,101.660004,100.779999,101.449997,101.820000,101.250000,101.660004,101.709999,101.779999,101.610001,101.769997,101.940002,101.839996,101.870003,101.970001,101.889999,101.830002</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.046402,0.094887,0.118134,0.581284,0.360191,0.488617,0.393364,2.125015,2.044815,2.859451,2.233566,1.910026,2.451981,1.882560,1.916138,1.804832,1.895279,1.565933,1.338356,1.368531,1.338882,1.164681,1.119423,1.337967</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.044746,0.091572,0.114029,0.556945,0.346204,0.469193,0.377944,2.091962,2.011426,2.837320,2.201642,1.875885,2.421710,1.851820,1.883923,1.773268,1.865249,1.538698,1.312886,1.343805,1.314305,1.142180,1.098658,1.313922</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.328303822680022</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>103.629822,103.748146,103.709869,103.606522,103.738678,103.700096,103.678177,103.704796,103.392723,103.666199,103.604843,103.710464,103.466187,103.820854,103.547554,103.382156,103.345665,103.125893,103.260559,103.073013,103.187263,103.044945,103.165329,102.993248</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>103.109024,102.985703,102.923149,102.978210,102.681396,102.549118,102.523918,102.406754,102.424149,102.242859,102.161110,102.055565,101.943710,101.554657,101.631790,101.609299,101.405502,101.089737,100.927567,100.876282,100.769051,100.463089,100.486343,100.657516</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:43</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>101.906670,101.881531,101.943886,101.982430,101.927437,101.911850,101.915733,101.878082,101.843140,101.734726,101.764854,101.757965,101.703537,101.629463,101.729744,101.670593,101.705139,101.609718,101.613686,101.586067,101.626259,101.579567,101.441597,101.558060</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>101.855766,101.915794,101.839821,101.957085,101.999878,101.946335,101.811295,101.650269,101.609184,101.907890,101.699280,101.686592,101.630295,101.822151,101.699989,101.611870,101.721115,101.624466,101.614845,101.609505,101.617867,101.509911,101.667435,101.471733</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>101.126518,101.115021,101.023552,101.199951,100.826340,100.678986,100.647598,100.573364,100.267418,100.031830,99.939049,99.829048,99.509560,99.432610,99.557899,99.541977,99.290466,99.172356,98.797722,98.754395,98.746750,98.606750,98.431793,98.437874</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>101.532524,101.413162,101.438812,101.472343,101.197342,101.141251,101.069435,100.958977,100.980217,100.767319,100.653961,100.448898,100.312851,100.164490,100.269012,100.292465,100.173286,99.951996,99.901573,99.932999,99.849358,99.632133,99.572250,99.723907</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>101.5580596923828</v>
+      </c>
+      <c r="G49" t="n">
+        <v>106.120002746582</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.561943054199233</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.298853124884759</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.552904169296135</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:33</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="n">
+        <v>104.8945617675781</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>101.906670,101.881531,101.943886,101.982430,101.927437,101.911850,101.915733,101.878082,101.843140,101.734726,101.764854,101.757965,101.703537,101.629463,101.729744,101.670593,101.705139,101.609718,101.613686,101.586067,101.626259,101.579567,101.441597,101.558060</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>101.889999,102.309998,102.250000,102.580002,102.540001,102.540001,102.339996,103.239998,102.660004,102.879997,102.959999,103.419998,104.260002,103.919998,103.419998,103.250000,103.739998,103.379997,103.260002,103.300003,104.059998,104.370003,105.970001,106.120003</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.016671,0.428467,0.306114,0.597572,0.612564,0.628151,0.424263,1.361916,0.816864,1.145271,1.195145,1.662033,2.556465,2.290535,1.690254,1.579407,2.034859,1.770279,1.646316,1.713936,2.433739,2.790436,4.528404,4.561943</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.016361,0.418792,0.299378,0.582542,0.597390,0.612591,0.414563,1.319175,0.795698,1.113211,1.160786,1.607071,2.452009,2.204133,1.634359,1.529692,1.961499,1.712400,1.594341,1.659183,2.338784,2.673599,4.273289,4.298853</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1.552904169296135</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>101.855766,101.915794,101.839821,101.957085,101.999878,101.946335,101.811295,101.650269,101.609184,101.907890,101.699280,101.686592,101.630295,101.822151,101.699989,101.611870,101.721115,101.624466,101.614845,101.609505,101.617867,101.509911,101.667435,101.471733</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>101.532524,101.413162,101.438812,101.472343,101.197342,101.141251,101.069435,100.958977,100.980217,100.767319,100.653961,100.448898,100.312851,100.164490,100.269012,100.292465,100.173286,99.951996,99.901573,99.932999,99.849358,99.632133,99.572250,99.723907</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:33</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>105.966263,105.979340,106.014717,106.070190,105.914513,105.827415,105.844772,105.712082,105.741852,105.646309,105.624069,105.619186,105.503540,105.367645,105.410393,105.332489,105.188080,105.061066,104.969696,104.953812,104.895592,104.851059,104.826225,104.894562</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>105.792793,105.894165,105.901428,105.901337,105.990585,105.681366,105.751709,105.664879,105.537720,105.577240,105.557068,105.284988,105.424904,105.457245,105.303612,105.288506,105.103409,104.934715,105.079132,104.920967,104.732689,104.817139,104.818657,104.719284</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>104.428818,104.262276,104.015823,104.253754,103.759315,103.475563,103.460800,103.302658,102.989830,102.793922,102.599060,102.496475,102.121216,102.084404,102.097061,102.163574,101.805717,101.645988,101.255692,101.262909,101.204407,101.159218,101.106171,101.085419</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>105.165359,105.012299,104.880051,104.997734,104.533432,104.383095,104.299797,104.148094,104.194878,103.985786,103.793770,103.600647,103.483551,103.204079,103.236633,103.299637,103.083092,102.799805,102.651199,102.702431,102.545883,102.435463,102.485611,102.637711</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>104.8945617675781</v>
+      </c>
+      <c r="G50" t="n">
+        <v>105.0500030517578</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1554412841797159</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1479688526073916</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.6047264232950706</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:52</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="n">
+        <v>104.2133941650391</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>105.966263,105.979340,106.014717,106.070190,105.914513,105.827415,105.844772,105.712082,105.741852,105.646309,105.624069,105.619186,105.503540,105.367645,105.410393,105.332489,105.188080,105.061066,104.969696,104.953812,104.895592,104.851059,104.826225,104.894562</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>106.370003,105.379997,105.290001,105.199997,106.500000,106.680000,106.459999,106.800003,107.080002,105.720001,105.739998,106.080002,106.199997,105.989998,105.489998,105.690002,105.919998,105.849998,106.559998,106.150002,105.330002,105.750000,104.949997,105.050003</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.403740,0.599343,0.724716,0.870193,0.585487,0.852585,0.615227,1.087921,1.338150,0.073692,0.115929,0.460816,0.696457,0.622353,0.079605,0.357513,0.731918,0.788932,1.590302,1.196190,0.434410,0.898941,0.123772,0.155441</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.379562,0.568744,0.688305,0.827180,0.549753,0.799199,0.577895,1.018653,1.249673,0.069705,0.109636,0.434404,0.655798,0.587181,0.075462,0.338266,0.691010,0.745331,1.492400,1.126886,0.412427,0.850062,0.117934,0.147969</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.6047264232950706</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>105.792793,105.894165,105.901428,105.901337,105.990585,105.681366,105.751709,105.664879,105.537720,105.577240,105.557068,105.284988,105.424904,105.457245,105.303612,105.288506,105.103409,104.934715,105.079132,104.920967,104.732689,104.817139,104.818657,104.719284</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>105.165359,105.012299,104.880051,104.997734,104.533432,104.383095,104.299797,104.148094,104.194878,103.985786,103.793770,103.600647,103.483551,103.204079,103.236633,103.299637,103.083092,102.799805,102.651199,102.702431,102.545883,102.435463,102.485611,102.637711</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:52</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>105.022507,104.875389,104.801346,104.863533,104.716919,104.735916,104.633606,104.612915,104.673363,104.569199,104.521614,104.580795,104.421021,104.238853,104.329781,104.317238,104.349503,104.292191,104.232468,104.253288,104.286774,104.181503,104.054642,104.213394</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>104.810066,104.672440,104.689346,104.974983,104.983391,104.591942,104.477280,104.606163,104.279419,104.420799,104.451828,104.393127,104.205780,104.427162,104.127289,104.178452,104.269165,104.056427,104.139305,104.208321,104.015572,104.073463,104.027534,103.951355</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>103.810387,103.620888,103.293701,103.396133,103.010361,102.629364,102.525085,102.439659,102.144569,101.895782,101.615242,101.661804,101.288559,101.021240,100.906105,100.919830,100.812340,100.651039,100.346436,100.208862,100.261192,100.181740,99.960938,99.969254</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>104.424469,104.127800,103.958702,103.974854,103.625832,103.409554,103.304596,103.174652,103.286026,103.092430,102.800774,102.745857,102.539688,102.210045,102.202980,102.270416,102.177727,101.990997,101.885170,101.932312,101.979424,101.547516,101.542839,101.682739</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>104.2133941650391</v>
+      </c>
+      <c r="G51" t="n">
+        <v>103.0599975585938</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.153396606445355</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.119150624653957</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.4311506054944478</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:37</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="n">
+        <v>102.6109924316406</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>105.022507,104.875389,104.801346,104.863533,104.716919,104.735916,104.633606,104.612915,104.673363,104.569199,104.521614,104.580795,104.421021,104.238853,104.329781,104.317238,104.349503,104.292191,104.232468,104.253288,104.286774,104.181503,104.054642,104.213394</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>105.139999,105.050003,104.470001,104.699997,104.650002,105.000000,104.919998,105.730003,105.089996,104.650002,103.220001,103.860001,103.989998,103.910004,104.370003,104.080002,103.889999,103.529999,103.790001,104.080002,104.349998,103.279999,103.330002,103.059998</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.117492,0.174614,0.331345,0.163536,0.066917,0.264084,0.286392,1.117088,0.416633,0.080803,1.301613,0.720794,0.431023,0.328849,0.040222,0.237236,0.459504,0.762192,0.442467,0.173286,0.063224,0.901504,0.724640,1.153396</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.111749,0.166220,0.317167,0.156195,0.063944,0.251509,0.272962,1.056548,0.396454,0.077212,1.261008,0.694006,0.414485,0.316475,0.038538,0.227936,0.442298,0.736204,0.426310,0.166493,0.060589,0.872874,0.701287,1.119150</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.4311506054944478</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>104.810066,104.672440,104.689346,104.974983,104.983391,104.591942,104.477280,104.606163,104.279419,104.420799,104.451828,104.393127,104.205780,104.427162,104.127289,104.178452,104.269165,104.056427,104.139305,104.208321,104.015572,104.073463,104.027534,103.951355</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>104.424469,104.127800,103.958702,103.974854,103.625832,103.409554,103.304596,103.174652,103.286026,103.092430,102.800774,102.745857,102.539688,102.210045,102.202980,102.270416,102.177727,101.990997,101.885170,101.932312,101.979424,101.547516,101.542839,101.682739</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:37</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>103.014282,102.919235,102.824799,102.874542,102.710762,102.798157,102.846420,102.755997,102.795174,102.735870,102.628815,102.650276,102.597427,102.476105,102.623497,102.581459,102.582428,102.561920,102.560120,102.571968,102.651901,102.652580,102.511261,102.610992</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>102.857590,102.727386,102.899956,103.058990,103.076965,102.859261,102.861916,102.792572,102.640335,102.675041,102.573074,102.634277,102.529480,102.831055,102.647560,102.407814,102.721626,102.716682,102.654694,102.555984,102.523849,102.557449,102.549026,102.552437</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>102.070023,101.940788,101.610107,101.725136,101.365517,101.191246,101.247681,101.088081,100.736473,100.628662,100.296471,100.411057,100.079681,99.865860,99.869408,99.789162,99.618561,99.548965,99.269463,99.224899,99.145691,99.136726,98.945045,98.924721</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>102.514275,102.298157,102.096542,102.081276,101.766968,101.707825,101.727783,101.552261,101.658897,101.472710,101.160347,101.195511,101.099159,100.750008,100.905090,100.815689,100.724487,100.578392,100.535042,100.554764,100.600952,100.334267,100.266273,100.349503</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>102.6109924316406</v>
+      </c>
+      <c r="G52" t="n">
+        <v>103.7699966430664</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.15900421142581</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.116897223589966</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.6665419892754317</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:15</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="n">
+        <v>103.4006652832031</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>103.014282,102.919235,102.824799,102.874542,102.710762,102.798157,102.846420,102.755997,102.795174,102.735870,102.628815,102.650276,102.597427,102.476105,102.623497,102.581459,102.582428,102.561920,102.560120,102.571968,102.651901,102.652580,102.511261,102.610992</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>102.949997,102.650002,102.919998,102.989998,103.680000,103.349998,102.839996,103.050003,102.669998,103.320000,104.279999,104.190002,103.690002,103.360001,103.230003,103.110001,103.029999,103.400002,103.370003,103.769997,103.800003,103.449997,103.309998,103.769997</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.064285,0.269233,0.095199,0.115456,0.969238,0.551841,0.006424,0.294006,0.125176,0.584130,1.651184,1.539726,1.092575,0.883896,0.606506,0.528542,0.447571,0.838082,0.809883,1.198029,1.148102,0.797417,0.798737,1.159005</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.062443,0.262283,0.092498,0.112104,0.934836,0.533954,0.006246,0.285304,0.121921,0.565360,1.583414,1.477806,1.053694,0.855162,0.587529,0.512600,0.434408,0.810524,0.783479,1.154504,1.106071,0.770824,0.773145,1.116898</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.6665419892754317</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>102.857590,102.727386,102.899956,103.058990,103.076965,102.859261,102.861916,102.792572,102.640335,102.675041,102.573074,102.634277,102.529480,102.831055,102.647560,102.407814,102.721626,102.716682,102.654694,102.555984,102.523849,102.557449,102.549026,102.552437</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>102.514275,102.298157,102.096542,102.081276,101.766968,101.707825,101.727783,101.552261,101.658897,101.472710,101.160347,101.195511,101.099159,100.750008,100.905090,100.815689,100.724487,100.578392,100.535042,100.554764,100.600952,100.334267,100.266273,100.349503</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:15</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>103.788925,103.743546,103.688286,103.770020,103.634872,103.737366,103.707436,103.719986,103.748795,103.678757,103.583786,103.687485,103.542938,103.475853,103.523483,103.485306,103.431152,103.398125,103.407654,103.397163,103.465744,103.378464,103.363243,103.400665</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>103.625626,103.449310,103.756096,103.756554,103.784676,103.661613,103.611908,103.737343,103.430939,103.581207,103.553322,103.445541,103.541603,103.712837,103.450027,103.216339,103.285042,103.467468,103.344879,103.149536,103.268356,103.189186,103.467079,103.379944</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>102.986832,102.904083,102.581749,102.759636,102.483246,102.374954,102.332191,102.285149,102.017609,101.887512,101.564995,101.649368,101.289070,101.269150,101.177872,101.177986,100.938477,100.850418,100.533699,100.475700,100.441093,100.368507,100.327202,100.260292</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>103.379745,103.254791,103.030212,103.105194,102.809059,102.803070,102.817871,102.770767,102.857079,102.680893,102.355888,102.419952,102.251015,102.043007,102.063400,102.087059,101.916496,101.758308,101.657257,101.662521,101.664719,101.468231,101.469055,101.563507</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>103.4006652832031</v>
+      </c>
+      <c r="G53" t="n">
+        <v>102.0599975585938</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.340667724609347</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.313607443346895</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.9375925278665728</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:04</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="n">
+        <v>101.588752746582</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>103.788925,103.743546,103.688286,103.770020,103.634872,103.737366,103.707436,103.719986,103.748795,103.678757,103.583786,103.687485,103.542938,103.475853,103.523483,103.485306,103.431152,103.398125,103.407654,103.397163,103.465744,103.378464,103.363243,103.400665</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>104.080002,104.500000,104.559998,104.820000,103.500000,103.790001,104.220001,104.639999,103.779999,103.459999,103.050003,103.389999,103.519997,103.260002,102.300003,102.550003,102.080002,100.800003,101.699997,100.980003,101.029999,101.849998,101.809998,102.059998</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.291077,0.756454,0.871712,1.049980,0.134872,0.052635,0.512565,0.920013,0.031204,0.218758,0.533783,0.297486,0.022941,0.215851,1.223480,0.935303,1.351150,2.598122,1.707657,2.417160,2.435745,1.528466,1.553245,1.340667</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.279666,0.723879,0.833695,1.001698,0.130311,0.050713,0.491811,0.879218,0.030067,0.211442,0.517984,0.287732,0.022161,0.209036,1.195973,0.912046,1.323619,2.577502,1.679112,2.393701,2.410913,1.500703,1.525632,1.313607</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.9375925278665728</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>103.625626,103.449310,103.756096,103.756554,103.784676,103.661613,103.611908,103.737343,103.430939,103.581207,103.553322,103.445541,103.541603,103.712837,103.450027,103.216339,103.285042,103.467468,103.344879,103.149536,103.268356,103.189186,103.467079,103.379944</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>103.379745,103.254791,103.030212,103.105194,102.809059,102.803070,102.817871,102.770767,102.857079,102.680893,102.355888,102.419952,102.251015,102.043007,102.063400,102.087059,101.916496,101.758308,101.657257,101.662521,101.664719,101.468231,101.469055,101.563507</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:04</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>101.859428,101.833336,101.756523,101.794693,101.638222,101.628296,101.564384,101.471474,101.571220,101.545410,101.402176,101.518486,101.467896,101.395447,101.421814,101.443871,101.473038,101.382736,101.519859,101.393791,101.508156,101.472687,101.509834,101.588753</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>101.728409,101.751190,101.673965,101.796066,101.809738,101.547363,101.481293,101.328369,101.406197,101.630035,101.290192,101.581085,101.529709,101.485184,101.397804,100.948090,101.270966,101.550003,101.604767,101.216934,101.377205,101.124329,101.481880,101.597122</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>100.960297,100.871735,100.568871,100.674057,100.346939,100.168877,100.080246,99.888290,99.781868,99.675529,99.341751,99.362091,99.180382,99.182518,99.086937,99.117767,98.934181,98.794327,98.586937,98.428749,98.605522,98.526772,98.540054,98.516167</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>101.373520,101.246147,101.025681,100.994263,100.723404,100.625595,100.521355,100.338295,100.539490,100.315376,99.989197,100.066612,100.033066,99.870407,99.929367,99.978867,99.858170,99.603012,99.656677,99.588882,99.673378,99.604698,99.608040,99.644714</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>101.588752746582</v>
+      </c>
+      <c r="G54" t="n">
+        <v>99.43000030517578</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.158752441406222</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.171127863603002</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.529963749023754</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:50</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="n">
+        <v>98.83963012695312</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>101.859428,101.833336,101.756523,101.794693,101.638222,101.628296,101.564384,101.471474,101.571220,101.545410,101.402176,101.518486,101.467896,101.395447,101.421814,101.443871,101.473038,101.382736,101.519859,101.393791,101.508156,101.472687,101.509834,101.588753</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>102.089996,101.919998,101.290001,101.139999,101.040001,101.019997,100.980003,98.889999,99.720001,100.169998,99.699997,99.629997,99.930000,99.889999,99.629997,100.019997,99.779999,99.250000,98.610001,99.120003,99.419998,99.279999,99.279999,99.430000</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0.230568,0.086662,0.466522,0.654694,0.598221,0.608299,0.584381,2.581475,1.851219,1.375412,1.702179,1.888489,1.537896,1.505448,1.791817,1.423874,1.693039,2.132736,2.909858,2.273788,2.088158,2.192688,2.229835,2.158753</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.225848,0.085030,0.460581,0.647314,0.592064,0.602157,0.578709,2.610451,1.856417,1.373078,1.707301,1.895502,1.538973,1.507105,1.798471,1.423590,1.696772,2.148852,2.950876,2.293975,2.100340,2.208590,2.246006,2.171128</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1.529963749023754</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>101.728409,101.751190,101.673965,101.796066,101.809738,101.547363,101.481293,101.328369,101.406197,101.630035,101.290192,101.581085,101.529709,101.485184,101.397804,100.948090,101.270966,101.550003,101.604767,101.216934,101.377205,101.124329,101.481880,101.597122</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>101.373520,101.246147,101.025681,100.994263,100.723404,100.625595,100.521355,100.338295,100.539490,100.315376,99.989197,100.066612,100.033066,99.870407,99.929367,99.978867,99.858170,99.603012,99.656677,99.588882,99.673378,99.604698,99.608040,99.644714</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:50</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>99.331482,99.339012,99.312706,99.387398,99.272629,99.286537,99.213112,99.177101,99.151825,99.093216,98.974205,99.068443,99.064407,99.023285,99.040092,99.039536,98.979729,99.013031,98.968559,98.867500,98.950806,98.855133,98.792404,98.839630</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>99.243774,99.272270,99.238998,99.432632,99.531631,99.190170,99.090088,99.127373,99.080437,99.142960,98.961258,99.037628,98.957970,99.194984,99.182999,98.788193,99.024902,99.316422,99.147614,98.721680,99.082878,98.685211,98.869225,98.789207</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>98.452934,98.373810,98.102272,98.284843,98.050156,98.003937,97.888611,97.737793,97.378128,97.221016,96.894585,97.043617,96.846413,96.789955,96.758636,96.676239,96.452957,96.384102,96.033051,95.910500,95.914024,95.844521,95.732033,95.629044</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>98.886978,98.723824,98.587761,98.614212,98.464073,98.409882,98.247101,98.120705,98.189522,97.978844,97.666916,97.753967,97.712723,97.589272,97.697899,97.643562,97.353600,97.295937,97.183159,97.150734,97.221733,96.912674,96.948135,96.916946</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>98.83963012695312</v>
+      </c>
+      <c r="G55" t="n">
+        <v>101.6100006103516</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.770370483398438</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.726474231628147</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.275118548356218</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>100.6736145019531</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>99.331482,99.339012,99.312706,99.387398,99.272629,99.286537,99.213112,99.177101,99.151825,99.093216,98.974205,99.068443,99.064407,99.023285,99.040092,99.039536,98.979729,99.013031,98.968559,98.867500,98.950806,98.855133,98.792404,98.839630</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>99.849998,99.790001,99.720001,99.889999,99.370003,99.160004,99.470001,101.639999,104.790001,103.269997,101.580002,102.320000,101.940002,101.029999,102.000000,102.449997,102.059998,101.839996,102.449997,101.900002,101.980003,101.870003,101.620003,101.610001</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.518516,0.450989,0.407295,0.502601,0.097374,0.126533,0.256889,2.462898,5.638176,4.176781,2.605797,3.251557,2.875595,2.006714,2.959908,3.410461,3.080269,2.826965,3.481438,3.032502,3.029197,3.014870,2.827599,2.770371</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.519295,0.451938,0.408439,0.503155,0.097991,0.127605,0.258258,2.423159,5.380452,4.044525,2.565266,3.177831,2.820870,1.986255,2.901871,3.328903,3.018096,2.775889,3.398183,2.975958,2.970384,2.959527,2.782522,2.726474</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2.275118548356218</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>99.243774,99.272270,99.238998,99.432632,99.531631,99.190170,99.090088,99.127373,99.080437,99.142960,98.961258,99.037628,98.957970,99.194984,99.182999,98.788193,99.024902,99.316422,99.147614,98.721680,99.082878,98.685211,98.869225,98.789207</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>98.886978,98.723824,98.587761,98.614212,98.464073,98.409882,98.247101,98.120705,98.189522,97.978844,97.666916,97.753967,97.712723,97.589272,97.697899,97.643562,97.353600,97.295937,97.183159,97.150734,97.221733,96.912674,96.948135,96.916946</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>101.551758,101.556938,101.493881,101.559296,101.438248,101.445770,101.394836,101.326973,101.285286,101.223007,101.143845,101.152176,101.101730,101.012505,101.031540,100.915871,100.962578,100.954422,100.907974,100.788704,100.799408,100.794807,100.665947,100.673615</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>101.345901,101.325012,101.620415,101.474876,101.454308,101.403008,101.221085,101.387627,101.014206,101.344254,101.171364,101.225151,100.906563,101.072052,101.177856,100.737900,100.894615,100.936356,100.810280,100.682236,100.767876,100.723534,100.670563,100.664749</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>100.623772,100.554504,100.192703,100.262993,100.033798,99.881950,99.622307,99.485718,99.213081,99.081841,98.750137,98.734039,98.566406,98.435539,98.407814,98.184471,98.042236,97.995720,97.619545,97.447128,97.433739,97.475029,97.293640,97.089905</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>101.064529,100.918495,100.711418,100.733192,100.478699,100.321075,100.174301,100.073166,100.120506,99.914787,99.655624,99.587959,99.564705,99.333130,99.422920,99.324951,99.127144,99.013550,98.888214,98.823105,98.855698,98.654495,98.601288,98.544571</t>
         </is>
       </c>
     </row>
